--- a/Licencias.xlsx
+++ b/Licencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juan.melendezm\OneDrive - Claro Cenam\DyF &amp; TD - Buscador OM\tNPS Diario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="113_{845E1943-7DD0-4E9A-8F0E-9372CC4413EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{93BB587D-C382-4248-8835-65AEBCEB71D6}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="113_{845E1943-7DD0-4E9A-8F0E-9372CC4413EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{26BCF6F0-6F3D-45D7-90AB-B0AEEBBBFB3E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6225" xr2:uid="{315E89AC-049D-4CBC-BBA0-977EA9B4CA5F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6085" uniqueCount="1686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6085" uniqueCount="1685">
   <si>
     <t>Operador</t>
   </si>
@@ -5065,9 +5065,6 @@
   </si>
   <si>
     <t>Leonel Orellana</t>
-  </si>
-  <si>
-    <t>leonel Orellana</t>
   </si>
   <si>
     <t>Guillermo Martinez</t>
@@ -5429,19 +5426,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8EB08BF9-3CAF-4F8A-B7BA-1AB6EAF2E4E2}" name="Tabla1" displayName="Tabla1" ref="A1:I788" totalsRowShown="0">
-  <autoFilter ref="A1:I788" xr:uid="{1EB77753-C704-4B73-9D4A-390072FC9037}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Erick Morales"/>
-        <filter val="Guillermo Martinez"/>
-        <filter val="Jaime Flores"/>
-        <filter val="Leonel Orellana"/>
-        <filter val="Nesting"/>
-        <filter val="Rodrigo Gómez"/>
-        <filter val="Soporte"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I788" xr:uid="{1EB77753-C704-4B73-9D4A-390072FC9037}"/>
   <sortState ref="A2:I784">
     <sortCondition descending="1" ref="F1:F784"/>
   </sortState>
@@ -5797,7 +5782,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1">
+    <row r="2" spans="1:9">
       <c r="A2" s="24" t="s">
         <v>322</v>
       </c>
@@ -5824,7 +5809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1">
+    <row r="3" spans="1:9">
       <c r="A3" s="23" t="s">
         <v>1560</v>
       </c>
@@ -5851,7 +5836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1">
+    <row r="4" spans="1:9">
       <c r="A4" s="24" t="s">
         <v>317</v>
       </c>
@@ -5878,7 +5863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1">
+    <row r="5" spans="1:9">
       <c r="A5" s="25" t="s">
         <v>314</v>
       </c>
@@ -5905,7 +5890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1">
+    <row r="6" spans="1:9">
       <c r="A6" s="24" t="s">
         <v>309</v>
       </c>
@@ -7390,7 +7375,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1">
+    <row r="61" spans="1:9">
       <c r="A61" s="33" t="s">
         <v>775</v>
       </c>
@@ -8092,7 +8077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1">
+    <row r="87" spans="1:9">
       <c r="A87" s="39" t="s">
         <v>1510</v>
       </c>
@@ -8985,7 +8970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1">
+    <row r="120" spans="1:9">
       <c r="A120" s="36" t="s">
         <v>1486</v>
       </c>
@@ -9851,7 +9836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1">
+    <row r="152" spans="1:9">
       <c r="A152" s="24" t="s">
         <v>1365</v>
       </c>
@@ -9878,7 +9863,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1">
+    <row r="153" spans="1:9">
       <c r="A153" s="25" t="s">
         <v>1368</v>
       </c>
@@ -9905,7 +9890,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1">
+    <row r="154" spans="1:9">
       <c r="A154" s="22" t="s">
         <v>141</v>
       </c>
@@ -9932,7 +9917,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1">
+    <row r="155" spans="1:9">
       <c r="A155" s="19" t="s">
         <v>139</v>
       </c>
@@ -9959,7 +9944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1">
+    <row r="156" spans="1:9">
       <c r="A156" s="22" t="s">
         <v>135</v>
       </c>
@@ -9986,7 +9971,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1">
+    <row r="157" spans="1:9">
       <c r="A157" s="19" t="s">
         <v>143</v>
       </c>
@@ -10056,7 +10041,7 @@
       <c r="E159" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F159" s="34" t="s">
+      <c r="F159" s="35" t="s">
         <v>1679</v>
       </c>
       <c r="G159" s="9" t="s">
@@ -10112,7 +10097,7 @@
       <c r="E161" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F161" s="34" t="s">
+      <c r="F161" s="35" t="s">
         <v>1679</v>
       </c>
       <c r="G161" s="9" t="s">
@@ -10166,7 +10151,7 @@
       <c r="E163" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F163" s="34" t="s">
+      <c r="F163" s="35" t="s">
         <v>1679</v>
       </c>
       <c r="G163" s="9" t="s">
@@ -10274,7 +10259,7 @@
       <c r="E167" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F167" s="34" t="s">
+      <c r="F167" s="35" t="s">
         <v>1679</v>
       </c>
       <c r="G167" s="9" t="s">
@@ -10382,8 +10367,8 @@
       <c r="E171" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F171" s="34" t="s">
-        <v>1680</v>
+      <c r="F171" s="35" t="s">
+        <v>1679</v>
       </c>
       <c r="G171" s="9" t="s">
         <v>96</v>
@@ -10410,7 +10395,7 @@
         <v>4</v>
       </c>
       <c r="F172" s="35" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="G172" s="6" t="s">
         <v>96</v>
@@ -10436,8 +10421,8 @@
       <c r="E173" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F173" s="34" t="s">
-        <v>1680</v>
+      <c r="F173" s="35" t="s">
+        <v>1679</v>
       </c>
       <c r="G173" s="9" t="s">
         <v>96</v>
@@ -10464,7 +10449,7 @@
         <v>4</v>
       </c>
       <c r="F174" s="35" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="G174" s="6" t="s">
         <v>96</v>
@@ -10490,7 +10475,7 @@
       <c r="E175" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F175" s="34" t="s">
+      <c r="F175" s="35" t="s">
         <v>1679</v>
       </c>
       <c r="G175" s="9" t="s">
@@ -10555,7 +10540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1">
+    <row r="178" spans="1:9">
       <c r="A178" s="22" t="s">
         <v>274</v>
       </c>
@@ -10584,7 +10569,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1">
+    <row r="179" spans="1:9">
       <c r="A179" s="19" t="s">
         <v>272</v>
       </c>
@@ -10611,7 +10596,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1">
+    <row r="180" spans="1:9">
       <c r="A180" s="22" t="s">
         <v>270</v>
       </c>
@@ -10638,7 +10623,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1">
+    <row r="181" spans="1:9">
       <c r="A181" s="19" t="s">
         <v>268</v>
       </c>
@@ -10665,7 +10650,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1">
+    <row r="182" spans="1:9">
       <c r="A182" s="22" t="s">
         <v>266</v>
       </c>
@@ -10692,7 +10677,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1">
+    <row r="183" spans="1:9">
       <c r="A183" s="19" t="s">
         <v>264</v>
       </c>
@@ -10719,7 +10704,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1">
+    <row r="184" spans="1:9">
       <c r="A184" s="22" t="s">
         <v>262</v>
       </c>
@@ -10748,7 +10733,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1">
+    <row r="185" spans="1:9">
       <c r="A185" s="19" t="s">
         <v>260</v>
       </c>
@@ -10777,7 +10762,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1">
+    <row r="186" spans="1:9">
       <c r="A186" s="22" t="s">
         <v>258</v>
       </c>
@@ -10804,7 +10789,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1">
+    <row r="187" spans="1:9">
       <c r="A187" s="19" t="s">
         <v>256</v>
       </c>
@@ -10831,7 +10816,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1">
+    <row r="188" spans="1:9">
       <c r="A188" s="22" t="s">
         <v>254</v>
       </c>
@@ -10858,7 +10843,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1">
+    <row r="189" spans="1:9">
       <c r="A189" s="19" t="s">
         <v>252</v>
       </c>
@@ -10885,7 +10870,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1">
+    <row r="190" spans="1:9">
       <c r="A190" s="22" t="s">
         <v>250</v>
       </c>
@@ -10912,7 +10897,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1">
+    <row r="191" spans="1:9">
       <c r="A191" s="19" t="s">
         <v>248</v>
       </c>
@@ -10939,7 +10924,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1">
+    <row r="192" spans="1:9">
       <c r="A192" s="22" t="s">
         <v>246</v>
       </c>
@@ -10966,7 +10951,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1">
+    <row r="193" spans="1:9">
       <c r="A193" s="19" t="s">
         <v>244</v>
       </c>
@@ -10993,7 +10978,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1">
+    <row r="194" spans="1:9">
       <c r="A194" s="22" t="s">
         <v>242</v>
       </c>
@@ -11020,7 +11005,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1">
+    <row r="195" spans="1:9">
       <c r="A195" s="19" t="s">
         <v>240</v>
       </c>
@@ -11047,7 +11032,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1">
+    <row r="196" spans="1:9">
       <c r="A196" s="22" t="s">
         <v>238</v>
       </c>
@@ -11074,7 +11059,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1">
+    <row r="197" spans="1:9">
       <c r="A197" s="19" t="s">
         <v>236</v>
       </c>
@@ -11101,7 +11086,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1">
+    <row r="198" spans="1:9">
       <c r="A198" s="22" t="s">
         <v>234</v>
       </c>
@@ -11128,7 +11113,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1">
+    <row r="199" spans="1:9">
       <c r="A199" s="19" t="s">
         <v>232</v>
       </c>
@@ -11155,7 +11140,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1">
+    <row r="200" spans="1:9">
       <c r="A200" s="22" t="s">
         <v>230</v>
       </c>
@@ -11182,7 +11167,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1">
+    <row r="201" spans="1:9">
       <c r="A201" s="19" t="s">
         <v>228</v>
       </c>
@@ -11209,7 +11194,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1">
+    <row r="202" spans="1:9">
       <c r="A202" s="22" t="s">
         <v>226</v>
       </c>
@@ -11238,7 +11223,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1">
+    <row r="203" spans="1:9">
       <c r="A203" s="19" t="s">
         <v>224</v>
       </c>
@@ -11265,7 +11250,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1">
+    <row r="204" spans="1:9">
       <c r="A204" s="22" t="s">
         <v>222</v>
       </c>
@@ -11292,7 +11277,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1">
+    <row r="205" spans="1:9">
       <c r="A205" s="19" t="s">
         <v>220</v>
       </c>
@@ -11319,7 +11304,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1">
+    <row r="206" spans="1:9">
       <c r="A206" s="22" t="s">
         <v>218</v>
       </c>
@@ -11346,7 +11331,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1">
+    <row r="207" spans="1:9">
       <c r="A207" s="19" t="s">
         <v>216</v>
       </c>
@@ -11375,7 +11360,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1">
+    <row r="208" spans="1:9">
       <c r="A208" s="22" t="s">
         <v>214</v>
       </c>
@@ -11402,7 +11387,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1">
+    <row r="209" spans="1:9">
       <c r="A209" s="19" t="s">
         <v>212</v>
       </c>
@@ -11429,7 +11414,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1">
+    <row r="210" spans="1:9">
       <c r="A210" s="22" t="s">
         <v>210</v>
       </c>
@@ -11456,7 +11441,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1">
+    <row r="211" spans="1:9">
       <c r="A211" s="19" t="s">
         <v>208</v>
       </c>
@@ -11483,7 +11468,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1">
+    <row r="212" spans="1:9">
       <c r="A212" s="22" t="s">
         <v>206</v>
       </c>
@@ -11512,7 +11497,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1">
+    <row r="213" spans="1:9">
       <c r="A213" s="19" t="s">
         <v>203</v>
       </c>
@@ -11539,7 +11524,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1">
+    <row r="214" spans="1:9">
       <c r="A214" s="22" t="s">
         <v>198</v>
       </c>
@@ -11566,7 +11551,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1">
+    <row r="215" spans="1:9">
       <c r="A215" s="19" t="s">
         <v>276</v>
       </c>
@@ -11593,7 +11578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1">
+    <row r="216" spans="1:9">
       <c r="A216" s="22" t="s">
         <v>286</v>
       </c>
@@ -11620,7 +11605,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1">
+    <row r="217" spans="1:9">
       <c r="A217" s="19" t="s">
         <v>284</v>
       </c>
@@ -11647,7 +11632,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1">
+    <row r="218" spans="1:9">
       <c r="A218" s="22" t="s">
         <v>282</v>
       </c>
@@ -11674,7 +11659,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1">
+    <row r="219" spans="1:9">
       <c r="A219" s="19" t="s">
         <v>279</v>
       </c>
@@ -11701,7 +11686,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1">
+    <row r="220" spans="1:9">
       <c r="A220" s="22" t="s">
         <v>293</v>
       </c>
@@ -11730,7 +11715,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1">
+    <row r="221" spans="1:9">
       <c r="A221" s="19" t="s">
         <v>288</v>
       </c>
@@ -11774,7 +11759,7 @@
         <v>4</v>
       </c>
       <c r="F222" s="6" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G222" s="6" t="s">
         <v>96</v>
@@ -11801,7 +11786,7 @@
         <v>4</v>
       </c>
       <c r="F223" s="9" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G223" s="9" t="s">
         <v>96</v>
@@ -11828,7 +11813,7 @@
         <v>4</v>
       </c>
       <c r="F224" s="6" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G224" s="6" t="s">
         <v>96</v>
@@ -11882,7 +11867,7 @@
         <v>4</v>
       </c>
       <c r="F226" s="6" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G226" s="6" t="s">
         <v>96</v>
@@ -11909,7 +11894,7 @@
         <v>4</v>
       </c>
       <c r="F227" s="9" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G227" s="9" t="s">
         <v>96</v>
@@ -11936,7 +11921,7 @@
         <v>4</v>
       </c>
       <c r="F228" s="6" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G228" s="6" t="s">
         <v>96</v>
@@ -11963,7 +11948,7 @@
         <v>4</v>
       </c>
       <c r="F229" s="9" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G229" s="9" t="s">
         <v>96</v>
@@ -11990,7 +11975,7 @@
         <v>4</v>
       </c>
       <c r="F230" s="6" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G230" s="6" t="s">
         <v>96</v>
@@ -12017,7 +12002,7 @@
         <v>4</v>
       </c>
       <c r="F231" s="9" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G231" s="9" t="s">
         <v>96</v>
@@ -12044,7 +12029,7 @@
         <v>4</v>
       </c>
       <c r="F232" s="6" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G232" s="6" t="s">
         <v>96</v>
@@ -12100,7 +12085,7 @@
         <v>4</v>
       </c>
       <c r="F234" s="6" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G234" s="6" t="s">
         <v>96</v>
@@ -12127,7 +12112,7 @@
         <v>4</v>
       </c>
       <c r="F235" s="9" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G235" s="9" t="s">
         <v>96</v>
@@ -12236,7 +12221,7 @@
       <c r="E239" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F239" s="9" t="s">
+      <c r="F239" s="35" t="s">
         <v>1679</v>
       </c>
       <c r="G239" s="9" t="s">
@@ -12264,7 +12249,7 @@
         <v>4</v>
       </c>
       <c r="F240" s="6" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G240" s="6" t="s">
         <v>96</v>
@@ -12291,7 +12276,7 @@
         <v>4</v>
       </c>
       <c r="F241" s="9" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G241" s="9" t="s">
         <v>96</v>
@@ -12301,7 +12286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1">
+    <row r="242" spans="1:9">
       <c r="A242" s="22" t="s">
         <v>1602</v>
       </c>
@@ -12345,7 +12330,7 @@
         <v>4</v>
       </c>
       <c r="F243" s="9" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G243" s="9" t="s">
         <v>96</v>
@@ -12355,7 +12340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1">
+    <row r="244" spans="1:9">
       <c r="A244" s="26" t="s">
         <v>307</v>
       </c>
@@ -12382,7 +12367,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1">
+    <row r="245" spans="1:9">
       <c r="A245" s="19" t="s">
         <v>305</v>
       </c>
@@ -12409,7 +12394,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1">
+    <row r="246" spans="1:9">
       <c r="A246" s="22" t="s">
         <v>303</v>
       </c>
@@ -12436,7 +12421,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1">
+    <row r="247" spans="1:9">
       <c r="A247" s="19" t="s">
         <v>301</v>
       </c>
@@ -12463,7 +12448,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1">
+    <row r="248" spans="1:9">
       <c r="A248" s="26" t="s">
         <v>299</v>
       </c>
@@ -12490,7 +12475,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1">
+    <row r="249" spans="1:9">
       <c r="A249" s="19" t="s">
         <v>297</v>
       </c>
@@ -12517,7 +12502,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1">
+    <row r="250" spans="1:9">
       <c r="A250" s="26" t="s">
         <v>81</v>
       </c>
@@ -12544,7 +12529,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1">
+    <row r="251" spans="1:9">
       <c r="A251" s="23" t="s">
         <v>295</v>
       </c>
@@ -12571,7 +12556,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1">
+    <row r="252" spans="1:9">
       <c r="A252" s="26" t="s">
         <v>323</v>
       </c>
@@ -12598,7 +12583,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1">
+    <row r="253" spans="1:9">
       <c r="A253" s="19" t="s">
         <v>321</v>
       </c>
@@ -12643,7 +12628,7 @@
       <c r="E254" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F254" s="6" t="s">
+      <c r="F254" s="35" t="s">
         <v>1679</v>
       </c>
       <c r="G254" s="6" t="s">
@@ -12654,7 +12639,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1">
+    <row r="255" spans="1:9">
       <c r="A255" s="23" t="s">
         <v>315</v>
       </c>
@@ -12681,7 +12666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1">
+    <row r="256" spans="1:9">
       <c r="A256" s="22" t="s">
         <v>312</v>
       </c>
@@ -12708,7 +12693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1">
+    <row r="257" spans="1:9">
       <c r="A257" s="19" t="s">
         <v>389</v>
       </c>
@@ -12737,7 +12722,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1">
+    <row r="258" spans="1:9">
       <c r="A258" s="26" t="s">
         <v>387</v>
       </c>
@@ -12766,7 +12751,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1">
+    <row r="259" spans="1:9">
       <c r="A259" s="19" t="s">
         <v>385</v>
       </c>
@@ -12793,7 +12778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1">
+    <row r="260" spans="1:9">
       <c r="A260" s="22" t="s">
         <v>383</v>
       </c>
@@ -12820,7 +12805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1">
+    <row r="261" spans="1:9">
       <c r="A261" s="19" t="s">
         <v>381</v>
       </c>
@@ -12847,7 +12832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1">
+    <row r="262" spans="1:9">
       <c r="A262" s="22" t="s">
         <v>379</v>
       </c>
@@ -12876,7 +12861,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1">
+    <row r="263" spans="1:9">
       <c r="A263" s="23" t="s">
         <v>377</v>
       </c>
@@ -12905,7 +12890,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1">
+    <row r="264" spans="1:9">
       <c r="A264" s="22" t="s">
         <v>375</v>
       </c>
@@ -12934,7 +12919,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1">
+    <row r="265" spans="1:9">
       <c r="A265" s="23" t="s">
         <v>373</v>
       </c>
@@ -12963,7 +12948,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1">
+    <row r="266" spans="1:9">
       <c r="A266" s="26" t="s">
         <v>371</v>
       </c>
@@ -12992,7 +12977,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1">
+    <row r="267" spans="1:9">
       <c r="A267" s="23" t="s">
         <v>369</v>
       </c>
@@ -13019,7 +13004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1">
+    <row r="268" spans="1:9">
       <c r="A268" s="22" t="s">
         <v>367</v>
       </c>
@@ -13046,7 +13031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1">
+    <row r="269" spans="1:9">
       <c r="A269" s="19" t="s">
         <v>365</v>
       </c>
@@ -13073,7 +13058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1">
+    <row r="270" spans="1:9">
       <c r="A270" s="26" t="s">
         <v>363</v>
       </c>
@@ -13102,7 +13087,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1">
+    <row r="271" spans="1:9">
       <c r="A271" s="23" t="s">
         <v>361</v>
       </c>
@@ -13131,7 +13116,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1">
+    <row r="272" spans="1:9">
       <c r="A272" s="22" t="s">
         <v>359</v>
       </c>
@@ -13160,7 +13145,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1">
+    <row r="273" spans="1:9">
       <c r="A273" s="23" t="s">
         <v>357</v>
       </c>
@@ -13187,7 +13172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1">
+    <row r="274" spans="1:9">
       <c r="A274" s="22" t="s">
         <v>355</v>
       </c>
@@ -13214,7 +13199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1">
+    <row r="275" spans="1:9">
       <c r="A275" s="19" t="s">
         <v>353</v>
       </c>
@@ -13243,7 +13228,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1">
+    <row r="276" spans="1:9">
       <c r="A276" s="26" t="s">
         <v>351</v>
       </c>
@@ -13270,7 +13255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1">
+    <row r="277" spans="1:9">
       <c r="A277" s="19" t="s">
         <v>349</v>
       </c>
@@ -13299,7 +13284,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1">
+    <row r="278" spans="1:9">
       <c r="A278" s="26" t="s">
         <v>347</v>
       </c>
@@ -13326,7 +13311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1">
+    <row r="279" spans="1:9">
       <c r="A279" s="23" t="s">
         <v>345</v>
       </c>
@@ -13355,7 +13340,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1">
+    <row r="280" spans="1:9">
       <c r="A280" s="26" t="s">
         <v>343</v>
       </c>
@@ -13384,7 +13369,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1">
+    <row r="281" spans="1:9">
       <c r="A281" s="23" t="s">
         <v>341</v>
       </c>
@@ -13413,7 +13398,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1">
+    <row r="282" spans="1:9">
       <c r="A282" s="26" t="s">
         <v>339</v>
       </c>
@@ -13442,7 +13427,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1">
+    <row r="283" spans="1:9">
       <c r="A283" s="19" t="s">
         <v>337</v>
       </c>
@@ -13469,7 +13454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1">
+    <row r="284" spans="1:9">
       <c r="A284" s="26" t="s">
         <v>335</v>
       </c>
@@ -13496,7 +13481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1">
+    <row r="285" spans="1:9">
       <c r="A285" s="19" t="s">
         <v>333</v>
       </c>
@@ -13525,7 +13510,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1">
+    <row r="286" spans="1:9">
       <c r="A286" s="26" t="s">
         <v>331</v>
       </c>
@@ -13552,7 +13537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1">
+    <row r="287" spans="1:9">
       <c r="A287" s="23" t="s">
         <v>329</v>
       </c>
@@ -13579,7 +13564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1">
+    <row r="288" spans="1:9">
       <c r="A288" s="26" t="s">
         <v>325</v>
       </c>
@@ -13608,7 +13593,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1">
+    <row r="289" spans="1:9">
       <c r="A289" s="19" t="s">
         <v>391</v>
       </c>
@@ -13637,7 +13622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1">
+    <row r="290" spans="1:9">
       <c r="A290" s="26" t="s">
         <v>405</v>
       </c>
@@ -13654,7 +13639,7 @@
         <v>327</v>
       </c>
       <c r="F290" s="6" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="G290" s="6" t="s">
         <v>96</v>
@@ -13664,7 +13649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1">
+    <row r="291" spans="1:9">
       <c r="A291" s="19" t="s">
         <v>403</v>
       </c>
@@ -13691,7 +13676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1">
+    <row r="292" spans="1:9">
       <c r="A292" s="26" t="s">
         <v>401</v>
       </c>
@@ -13718,7 +13703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1">
+    <row r="293" spans="1:9">
       <c r="A293" s="19" t="s">
         <v>399</v>
       </c>
@@ -13745,7 +13730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1">
+    <row r="294" spans="1:9">
       <c r="A294" s="26" t="s">
         <v>397</v>
       </c>
@@ -13774,7 +13759,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1">
+    <row r="295" spans="1:9">
       <c r="A295" s="23" t="s">
         <v>394</v>
       </c>
@@ -13801,7 +13786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1">
+    <row r="296" spans="1:9">
       <c r="A296" s="22" t="s">
         <v>407</v>
       </c>
@@ -13828,7 +13813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1">
+    <row r="297" spans="1:9">
       <c r="A297" s="23" t="s">
         <v>127</v>
       </c>
@@ -13855,7 +13840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1">
+    <row r="298" spans="1:9">
       <c r="A298" s="26" t="s">
         <v>125</v>
       </c>
@@ -13882,7 +13867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1">
+    <row r="299" spans="1:9">
       <c r="A299" s="23" t="s">
         <v>120</v>
       </c>
@@ -13909,7 +13894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1">
+    <row r="300" spans="1:9">
       <c r="A300" s="22" t="s">
         <v>1647</v>
       </c>
@@ -13936,7 +13921,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1">
+    <row r="301" spans="1:9">
       <c r="A301" s="19" t="s">
         <v>410</v>
       </c>
@@ -13965,7 +13950,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1">
+    <row r="302" spans="1:9">
       <c r="A302" s="22" t="s">
         <v>413</v>
       </c>
@@ -13992,7 +13977,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1">
+    <row r="303" spans="1:9">
       <c r="A303" s="19" t="s">
         <v>416</v>
       </c>
@@ -14019,7 +14004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1">
+    <row r="304" spans="1:9">
       <c r="A304" s="22" t="s">
         <v>420</v>
       </c>
@@ -14046,7 +14031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1">
+    <row r="305" spans="1:9">
       <c r="A305" s="23" t="s">
         <v>439</v>
       </c>
@@ -14073,7 +14058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1">
+    <row r="306" spans="1:9">
       <c r="A306" s="26" t="s">
         <v>437</v>
       </c>
@@ -14100,7 +14085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:9" hidden="1">
+    <row r="307" spans="1:9">
       <c r="A307" s="23" t="s">
         <v>435</v>
       </c>
@@ -14127,7 +14112,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="308" spans="1:9" hidden="1">
+    <row r="308" spans="1:9">
       <c r="A308" s="26" t="s">
         <v>433</v>
       </c>
@@ -14156,7 +14141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1">
+    <row r="309" spans="1:9">
       <c r="A309" s="23" t="s">
         <v>431</v>
       </c>
@@ -14183,7 +14168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1">
+    <row r="310" spans="1:9">
       <c r="A310" s="26" t="s">
         <v>429</v>
       </c>
@@ -14210,7 +14195,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1">
+    <row r="311" spans="1:9">
       <c r="A311" s="23" t="s">
         <v>427</v>
       </c>
@@ -14237,7 +14222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1">
+    <row r="312" spans="1:9">
       <c r="A312" s="26" t="s">
         <v>423</v>
       </c>
@@ -14264,7 +14249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1">
+    <row r="313" spans="1:9">
       <c r="A313" s="19" t="s">
         <v>496</v>
       </c>
@@ -14291,7 +14276,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1">
+    <row r="314" spans="1:9">
       <c r="A314" s="22" t="s">
         <v>494</v>
       </c>
@@ -14318,7 +14303,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1">
+    <row r="315" spans="1:9">
       <c r="A315" s="19" t="s">
         <v>492</v>
       </c>
@@ -14345,7 +14330,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1">
+    <row r="316" spans="1:9">
       <c r="A316" s="22" t="s">
         <v>1293</v>
       </c>
@@ -14372,7 +14357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1">
+    <row r="317" spans="1:9">
       <c r="A317" s="19" t="s">
         <v>490</v>
       </c>
@@ -14401,7 +14386,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1">
+    <row r="318" spans="1:9">
       <c r="A318" s="22" t="s">
         <v>1295</v>
       </c>
@@ -14430,7 +14415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:9" hidden="1">
+    <row r="319" spans="1:9">
       <c r="A319" s="19" t="s">
         <v>488</v>
       </c>
@@ -14457,7 +14442,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1">
+    <row r="320" spans="1:9">
       <c r="A320" s="22" t="s">
         <v>486</v>
       </c>
@@ -14484,7 +14469,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="321" spans="1:9" hidden="1">
+    <row r="321" spans="1:9">
       <c r="A321" s="19" t="s">
         <v>1297</v>
       </c>
@@ -14511,7 +14496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:9" hidden="1">
+    <row r="322" spans="1:9">
       <c r="A322" s="22" t="s">
         <v>484</v>
       </c>
@@ -14538,7 +14523,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="323" spans="1:9" hidden="1">
+    <row r="323" spans="1:9">
       <c r="A323" s="19" t="s">
         <v>1299</v>
       </c>
@@ -14565,7 +14550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:9" hidden="1">
+    <row r="324" spans="1:9">
       <c r="A324" s="22" t="s">
         <v>1301</v>
       </c>
@@ -14592,7 +14577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:9" hidden="1">
+    <row r="325" spans="1:9">
       <c r="A325" s="19" t="s">
         <v>482</v>
       </c>
@@ -14619,7 +14604,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="326" spans="1:9" hidden="1">
+    <row r="326" spans="1:9">
       <c r="A326" s="22" t="s">
         <v>480</v>
       </c>
@@ -14646,7 +14631,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="327" spans="1:9" hidden="1">
+    <row r="327" spans="1:9">
       <c r="A327" s="19" t="s">
         <v>478</v>
       </c>
@@ -14673,7 +14658,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="328" spans="1:9" hidden="1">
+    <row r="328" spans="1:9">
       <c r="A328" s="22" t="s">
         <v>476</v>
       </c>
@@ -14702,7 +14687,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="329" spans="1:9" hidden="1">
+    <row r="329" spans="1:9">
       <c r="A329" s="19" t="s">
         <v>1303</v>
       </c>
@@ -14729,7 +14714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1">
+    <row r="330" spans="1:9">
       <c r="A330" s="22" t="s">
         <v>1305</v>
       </c>
@@ -14756,7 +14741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:9" hidden="1">
+    <row r="331" spans="1:9">
       <c r="A331" s="19" t="s">
         <v>474</v>
       </c>
@@ -14783,7 +14768,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1">
+    <row r="332" spans="1:9">
       <c r="A332" s="22" t="s">
         <v>472</v>
       </c>
@@ -14810,7 +14795,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="333" spans="1:9" hidden="1">
+    <row r="333" spans="1:9">
       <c r="A333" s="19" t="s">
         <v>1307</v>
       </c>
@@ -14837,7 +14822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:9" hidden="1">
+    <row r="334" spans="1:9">
       <c r="A334" s="22" t="s">
         <v>470</v>
       </c>
@@ -14864,7 +14849,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="335" spans="1:9" hidden="1">
+    <row r="335" spans="1:9">
       <c r="A335" s="19" t="s">
         <v>468</v>
       </c>
@@ -14891,7 +14876,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="336" spans="1:9" hidden="1">
+    <row r="336" spans="1:9">
       <c r="A336" s="22" t="s">
         <v>1309</v>
       </c>
@@ -14918,7 +14903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1">
+    <row r="337" spans="1:9">
       <c r="A337" s="19" t="s">
         <v>466</v>
       </c>
@@ -14945,7 +14930,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1">
+    <row r="338" spans="1:9">
       <c r="A338" s="22" t="s">
         <v>1311</v>
       </c>
@@ -14972,7 +14957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1">
+    <row r="339" spans="1:9">
       <c r="A339" s="19" t="s">
         <v>464</v>
       </c>
@@ -14999,7 +14984,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1">
+    <row r="340" spans="1:9">
       <c r="A340" s="22" t="s">
         <v>1313</v>
       </c>
@@ -15026,7 +15011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:9" hidden="1">
+    <row r="341" spans="1:9">
       <c r="A341" s="19" t="s">
         <v>1315</v>
       </c>
@@ -15053,7 +15038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:9" hidden="1">
+    <row r="342" spans="1:9">
       <c r="A342" s="22" t="s">
         <v>462</v>
       </c>
@@ -15080,7 +15065,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="343" spans="1:9" hidden="1">
+    <row r="343" spans="1:9">
       <c r="A343" s="19" t="s">
         <v>460</v>
       </c>
@@ -15107,7 +15092,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1">
+    <row r="344" spans="1:9">
       <c r="A344" s="22" t="s">
         <v>458</v>
       </c>
@@ -15134,7 +15119,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1">
+    <row r="345" spans="1:9">
       <c r="A345" s="19" t="s">
         <v>1317</v>
       </c>
@@ -15161,7 +15146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1">
+    <row r="346" spans="1:9">
       <c r="A346" s="22" t="s">
         <v>456</v>
       </c>
@@ -15188,7 +15173,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1">
+    <row r="347" spans="1:9">
       <c r="A347" s="19" t="s">
         <v>1319</v>
       </c>
@@ -15215,7 +15200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1">
+    <row r="348" spans="1:9">
       <c r="A348" s="26" t="s">
         <v>454</v>
       </c>
@@ -15242,7 +15227,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1">
+    <row r="349" spans="1:9">
       <c r="A349" s="19" t="s">
         <v>1321</v>
       </c>
@@ -15269,7 +15254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1">
+    <row r="350" spans="1:9">
       <c r="A350" s="22" t="s">
         <v>1323</v>
       </c>
@@ -15296,7 +15281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1">
+    <row r="351" spans="1:9">
       <c r="A351" s="19" t="s">
         <v>1325</v>
       </c>
@@ -15323,7 +15308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1">
+    <row r="352" spans="1:9">
       <c r="A352" s="22" t="s">
         <v>452</v>
       </c>
@@ -15350,7 +15335,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1">
+    <row r="353" spans="1:9">
       <c r="A353" s="19" t="s">
         <v>450</v>
       </c>
@@ -15377,7 +15362,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1">
+    <row r="354" spans="1:9">
       <c r="A354" s="22" t="s">
         <v>1327</v>
       </c>
@@ -15404,7 +15389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1">
+    <row r="355" spans="1:9">
       <c r="A355" s="19" t="s">
         <v>448</v>
       </c>
@@ -15431,7 +15416,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="356" spans="1:9" hidden="1">
+    <row r="356" spans="1:9">
       <c r="A356" s="22" t="s">
         <v>1329</v>
       </c>
@@ -15458,7 +15443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1">
+    <row r="357" spans="1:9">
       <c r="A357" s="19" t="s">
         <v>446</v>
       </c>
@@ -15487,7 +15472,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="358" spans="1:9" hidden="1">
+    <row r="358" spans="1:9">
       <c r="A358" s="22" t="s">
         <v>444</v>
       </c>
@@ -15514,7 +15499,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1">
+    <row r="359" spans="1:9">
       <c r="A359" s="19" t="s">
         <v>441</v>
       </c>
@@ -15844,7 +15829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:9" hidden="1">
+    <row r="371" spans="1:9">
       <c r="A371" s="19" t="s">
         <v>559</v>
       </c>
@@ -15871,7 +15856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:9" hidden="1">
+    <row r="372" spans="1:9">
       <c r="A372" s="22" t="s">
         <v>557</v>
       </c>
@@ -15898,7 +15883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:9" hidden="1">
+    <row r="373" spans="1:9">
       <c r="A373" s="23" t="s">
         <v>555</v>
       </c>
@@ -15925,7 +15910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:9" hidden="1">
+    <row r="374" spans="1:9">
       <c r="A374" s="22" t="s">
         <v>553</v>
       </c>
@@ -15952,7 +15937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:9" hidden="1">
+    <row r="375" spans="1:9">
       <c r="A375" s="19" t="s">
         <v>551</v>
       </c>
@@ -15979,7 +15964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:9" hidden="1">
+    <row r="376" spans="1:9">
       <c r="A376" s="22" t="s">
         <v>549</v>
       </c>
@@ -16006,7 +15991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:9" hidden="1">
+    <row r="377" spans="1:9">
       <c r="A377" s="19" t="s">
         <v>546</v>
       </c>
@@ -16033,7 +16018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:9" hidden="1">
+    <row r="378" spans="1:9">
       <c r="A378" s="26" t="s">
         <v>651</v>
       </c>
@@ -16060,7 +16045,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="379" spans="1:9" hidden="1">
+    <row r="379" spans="1:9">
       <c r="A379" s="19" t="s">
         <v>643</v>
       </c>
@@ -16087,7 +16072,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="380" spans="1:9" hidden="1">
+    <row r="380" spans="1:9">
       <c r="A380" s="22" t="s">
         <v>639</v>
       </c>
@@ -16114,7 +16099,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="381" spans="1:9" hidden="1">
+    <row r="381" spans="1:9">
       <c r="A381" s="19" t="s">
         <v>623</v>
       </c>
@@ -16141,7 +16126,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="382" spans="1:9" hidden="1">
+    <row r="382" spans="1:9">
       <c r="A382" s="22" t="s">
         <v>613</v>
       </c>
@@ -16168,7 +16153,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="383" spans="1:9" hidden="1">
+    <row r="383" spans="1:9">
       <c r="A383" s="19" t="s">
         <v>498</v>
       </c>
@@ -16195,7 +16180,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="384" spans="1:9" hidden="1">
+    <row r="384" spans="1:9">
       <c r="A384" s="24" t="s">
         <v>1401</v>
       </c>
@@ -16222,7 +16207,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1">
+    <row r="385" spans="1:9">
       <c r="A385" s="25" t="s">
         <v>1407</v>
       </c>
@@ -16249,7 +16234,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1">
+    <row r="386" spans="1:9">
       <c r="A386" s="24" t="s">
         <v>1403</v>
       </c>
@@ -16276,7 +16261,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1">
+    <row r="387" spans="1:9">
       <c r="A387" s="25" t="s">
         <v>1405</v>
       </c>
@@ -16303,7 +16288,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="388" spans="1:9" hidden="1">
+    <row r="388" spans="1:9">
       <c r="A388" s="24" t="s">
         <v>1399</v>
       </c>
@@ -16330,7 +16315,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="389" spans="1:9" hidden="1">
+    <row r="389" spans="1:9">
       <c r="A389" s="25" t="s">
         <v>1397</v>
       </c>
@@ -16357,7 +16342,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1">
+    <row r="390" spans="1:9">
       <c r="A390" s="24" t="s">
         <v>1395</v>
       </c>
@@ -16384,7 +16369,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="391" spans="1:9" hidden="1">
+    <row r="391" spans="1:9">
       <c r="A391" s="30" t="s">
         <v>594</v>
       </c>
@@ -16411,7 +16396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1">
+    <row r="392" spans="1:9">
       <c r="A392" s="30" t="s">
         <v>45</v>
       </c>
@@ -16440,7 +16425,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="393" spans="1:9" hidden="1">
+    <row r="393" spans="1:9">
       <c r="A393" s="19" t="s">
         <v>20</v>
       </c>
@@ -16467,7 +16452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1">
+    <row r="394" spans="1:9">
       <c r="A394" s="24" t="s">
         <v>22</v>
       </c>
@@ -16496,7 +16481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:9" hidden="1">
+    <row r="395" spans="1:9">
       <c r="A395" s="25" t="s">
         <v>23</v>
       </c>
@@ -16523,7 +16508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:9" hidden="1">
+    <row r="396" spans="1:9">
       <c r="A396" s="24" t="s">
         <v>602</v>
       </c>
@@ -16577,7 +16562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:9" hidden="1">
+    <row r="398" spans="1:9">
       <c r="A398" s="24" t="s">
         <v>42</v>
       </c>
@@ -16604,7 +16589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:9" hidden="1">
+    <row r="399" spans="1:9">
       <c r="A399" s="25" t="s">
         <v>44</v>
       </c>
@@ -16658,7 +16643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:9" hidden="1">
+    <row r="401" spans="1:9">
       <c r="A401" s="25" t="s">
         <v>53</v>
       </c>
@@ -16685,7 +16670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:9" hidden="1">
+    <row r="402" spans="1:9">
       <c r="A402" s="24" t="s">
         <v>26</v>
       </c>
@@ -16712,7 +16697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:9" hidden="1">
+    <row r="403" spans="1:9">
       <c r="A403" s="25" t="s">
         <v>11</v>
       </c>
@@ -16739,7 +16724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:9" hidden="1">
+    <row r="404" spans="1:9">
       <c r="A404" s="24" t="s">
         <v>28</v>
       </c>
@@ -16766,7 +16751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:9" hidden="1">
+    <row r="405" spans="1:9">
       <c r="A405" s="25" t="s">
         <v>29</v>
       </c>
@@ -16793,7 +16778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:9" hidden="1">
+    <row r="406" spans="1:9">
       <c r="A406" s="24" t="s">
         <v>48</v>
       </c>
@@ -16820,7 +16805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:9" hidden="1">
+    <row r="407" spans="1:9">
       <c r="A407" s="25" t="s">
         <v>580</v>
       </c>
@@ -16847,7 +16832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:9" hidden="1">
+    <row r="408" spans="1:9">
       <c r="A408" s="24" t="s">
         <v>62</v>
       </c>
@@ -16874,7 +16859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:9" hidden="1">
+    <row r="409" spans="1:9">
       <c r="A409" s="25" t="s">
         <v>61</v>
       </c>
@@ -16901,7 +16886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:9" hidden="1">
+    <row r="410" spans="1:9">
       <c r="A410" s="24" t="s">
         <v>63</v>
       </c>
@@ -16928,7 +16913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:9" hidden="1">
+    <row r="411" spans="1:9">
       <c r="A411" s="25" t="s">
         <v>15</v>
       </c>
@@ -16955,7 +16940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:9" hidden="1">
+    <row r="412" spans="1:9">
       <c r="A412" s="24" t="s">
         <v>577</v>
       </c>
@@ -16982,7 +16967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:9" hidden="1">
+    <row r="413" spans="1:9">
       <c r="A413" s="25" t="s">
         <v>31</v>
       </c>
@@ -17009,7 +16994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:9" hidden="1">
+    <row r="414" spans="1:9">
       <c r="A414" s="24" t="s">
         <v>18</v>
       </c>
@@ -17036,7 +17021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:9" hidden="1">
+    <row r="415" spans="1:9">
       <c r="A415" s="19" t="s">
         <v>689</v>
       </c>
@@ -17063,7 +17048,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="416" spans="1:9" hidden="1">
+    <row r="416" spans="1:9">
       <c r="A416" s="22" t="s">
         <v>687</v>
       </c>
@@ -17090,7 +17075,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="417" spans="1:9" hidden="1">
+    <row r="417" spans="1:9">
       <c r="A417" s="19" t="s">
         <v>685</v>
       </c>
@@ -17117,7 +17102,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="418" spans="1:9" hidden="1">
+    <row r="418" spans="1:9">
       <c r="A418" s="22" t="s">
         <v>683</v>
       </c>
@@ -17144,7 +17129,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="419" spans="1:9" hidden="1">
+    <row r="419" spans="1:9">
       <c r="A419" s="19" t="s">
         <v>681</v>
       </c>
@@ -17171,7 +17156,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="420" spans="1:9" hidden="1">
+    <row r="420" spans="1:9">
       <c r="A420" s="22" t="s">
         <v>679</v>
       </c>
@@ -17198,7 +17183,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="421" spans="1:9" hidden="1">
+    <row r="421" spans="1:9">
       <c r="A421" s="19" t="s">
         <v>677</v>
       </c>
@@ -17225,7 +17210,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="422" spans="1:9" hidden="1">
+    <row r="422" spans="1:9">
       <c r="A422" s="22" t="s">
         <v>675</v>
       </c>
@@ -17252,7 +17237,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="423" spans="1:9" hidden="1">
+    <row r="423" spans="1:9">
       <c r="A423" s="23" t="s">
         <v>673</v>
       </c>
@@ -17279,7 +17264,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="424" spans="1:9" hidden="1">
+    <row r="424" spans="1:9">
       <c r="A424" s="22" t="s">
         <v>671</v>
       </c>
@@ -17306,7 +17291,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="425" spans="1:9" hidden="1">
+    <row r="425" spans="1:9">
       <c r="A425" s="19" t="s">
         <v>669</v>
       </c>
@@ -17333,7 +17318,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="426" spans="1:9" hidden="1">
+    <row r="426" spans="1:9">
       <c r="A426" s="22" t="s">
         <v>667</v>
       </c>
@@ -17360,7 +17345,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="427" spans="1:9" hidden="1">
+    <row r="427" spans="1:9">
       <c r="A427" s="19" t="s">
         <v>665</v>
       </c>
@@ -17387,7 +17372,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="428" spans="1:9" hidden="1">
+    <row r="428" spans="1:9">
       <c r="A428" s="22" t="s">
         <v>663</v>
       </c>
@@ -17414,7 +17399,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="429" spans="1:9" hidden="1">
+    <row r="429" spans="1:9">
       <c r="A429" s="19" t="s">
         <v>661</v>
       </c>
@@ -17441,7 +17426,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="430" spans="1:9" hidden="1">
+    <row r="430" spans="1:9">
       <c r="A430" s="22" t="s">
         <v>659</v>
       </c>
@@ -17468,7 +17453,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="431" spans="1:9" hidden="1">
+    <row r="431" spans="1:9">
       <c r="A431" s="19" t="s">
         <v>657</v>
       </c>
@@ -17495,7 +17480,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="432" spans="1:9" hidden="1">
+    <row r="432" spans="1:9">
       <c r="A432" s="22" t="s">
         <v>655</v>
       </c>
@@ -17522,7 +17507,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="433" spans="1:9" hidden="1">
+    <row r="433" spans="1:9">
       <c r="A433" s="19" t="s">
         <v>653</v>
       </c>
@@ -17549,7 +17534,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="434" spans="1:9" hidden="1">
+    <row r="434" spans="1:9">
       <c r="A434" s="22" t="s">
         <v>649</v>
       </c>
@@ -17576,7 +17561,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="435" spans="1:9" hidden="1">
+    <row r="435" spans="1:9">
       <c r="A435" s="19" t="s">
         <v>647</v>
       </c>
@@ -17603,7 +17588,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="436" spans="1:9" hidden="1">
+    <row r="436" spans="1:9">
       <c r="A436" s="22" t="s">
         <v>645</v>
       </c>
@@ -17630,7 +17615,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="437" spans="1:9" hidden="1">
+    <row r="437" spans="1:9">
       <c r="A437" s="19" t="s">
         <v>641</v>
       </c>
@@ -17657,7 +17642,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="438" spans="1:9" hidden="1">
+    <row r="438" spans="1:9">
       <c r="A438" s="22" t="s">
         <v>637</v>
       </c>
@@ -17684,7 +17669,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="439" spans="1:9" hidden="1">
+    <row r="439" spans="1:9">
       <c r="A439" s="19" t="s">
         <v>635</v>
       </c>
@@ -17711,7 +17696,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="440" spans="1:9" hidden="1">
+    <row r="440" spans="1:9">
       <c r="A440" s="22" t="s">
         <v>633</v>
       </c>
@@ -17738,7 +17723,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="441" spans="1:9" hidden="1">
+    <row r="441" spans="1:9">
       <c r="A441" s="23" t="s">
         <v>631</v>
       </c>
@@ -17765,7 +17750,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="442" spans="1:9" hidden="1">
+    <row r="442" spans="1:9">
       <c r="A442" s="26" t="s">
         <v>629</v>
       </c>
@@ -17792,7 +17777,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="443" spans="1:9" hidden="1">
+    <row r="443" spans="1:9">
       <c r="A443" s="19" t="s">
         <v>627</v>
       </c>
@@ -17819,7 +17804,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="444" spans="1:9" hidden="1">
+    <row r="444" spans="1:9">
       <c r="A444" s="22" t="s">
         <v>625</v>
       </c>
@@ -17846,7 +17831,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="445" spans="1:9" hidden="1">
+    <row r="445" spans="1:9">
       <c r="A445" s="19" t="s">
         <v>107</v>
       </c>
@@ -17873,7 +17858,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="446" spans="1:9" hidden="1">
+    <row r="446" spans="1:9">
       <c r="A446" s="22" t="s">
         <v>621</v>
       </c>
@@ -17900,7 +17885,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="447" spans="1:9" hidden="1">
+    <row r="447" spans="1:9">
       <c r="A447" s="19" t="s">
         <v>619</v>
       </c>
@@ -17927,7 +17912,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="448" spans="1:9" hidden="1">
+    <row r="448" spans="1:9">
       <c r="A448" s="22" t="s">
         <v>617</v>
       </c>
@@ -17954,7 +17939,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="449" spans="1:9" hidden="1">
+    <row r="449" spans="1:9">
       <c r="A449" s="19" t="s">
         <v>615</v>
       </c>
@@ -17981,7 +17966,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="450" spans="1:9" hidden="1">
+    <row r="450" spans="1:9">
       <c r="A450" s="22" t="s">
         <v>611</v>
       </c>
@@ -18008,7 +17993,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="451" spans="1:9" hidden="1">
+    <row r="451" spans="1:9">
       <c r="A451" s="19" t="s">
         <v>1415</v>
       </c>
@@ -18035,7 +18020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:9" hidden="1">
+    <row r="452" spans="1:9">
       <c r="A452" s="22" t="s">
         <v>520</v>
       </c>
@@ -18062,7 +18047,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="453" spans="1:9" hidden="1">
+    <row r="453" spans="1:9">
       <c r="A453" s="19" t="s">
         <v>1413</v>
       </c>
@@ -18089,7 +18074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:9" hidden="1">
+    <row r="454" spans="1:9">
       <c r="A454" s="24" t="s">
         <v>73</v>
       </c>
@@ -18118,7 +18103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:9" hidden="1">
+    <row r="455" spans="1:9">
       <c r="A455" s="25" t="s">
         <v>50</v>
       </c>
@@ -18145,7 +18130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:9" hidden="1">
+    <row r="456" spans="1:9">
       <c r="A456" s="24" t="s">
         <v>38</v>
       </c>
@@ -18172,7 +18157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:9" hidden="1">
+    <row r="457" spans="1:9">
       <c r="A457" s="23" t="s">
         <v>1274</v>
       </c>
@@ -18195,13 +18180,13 @@
         <v>178</v>
       </c>
       <c r="H457" s="9" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="I457" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:9" hidden="1">
+    <row r="458" spans="1:9">
       <c r="A458" s="26" t="s">
         <v>1265</v>
       </c>
@@ -18228,7 +18213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:9" hidden="1">
+    <row r="459" spans="1:9">
       <c r="A459" s="25" t="s">
         <v>701</v>
       </c>
@@ -18255,7 +18240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:9" hidden="1">
+    <row r="460" spans="1:9">
       <c r="A460" s="24" t="s">
         <v>66</v>
       </c>
@@ -18282,7 +18267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:9" hidden="1">
+    <row r="461" spans="1:9">
       <c r="A461" s="23" t="s">
         <v>1229</v>
       </c>
@@ -18305,13 +18290,13 @@
         <v>178</v>
       </c>
       <c r="H461" s="9" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="I461" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:9" hidden="1">
+    <row r="462" spans="1:9">
       <c r="A462" s="26" t="s">
         <v>1221</v>
       </c>
@@ -18338,7 +18323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:9" hidden="1">
+    <row r="463" spans="1:9">
       <c r="A463" s="25" t="s">
         <v>67</v>
       </c>
@@ -18365,7 +18350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:9" hidden="1">
+    <row r="464" spans="1:9">
       <c r="A464" s="24" t="s">
         <v>71</v>
       </c>
@@ -18394,7 +18379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:9" hidden="1">
+    <row r="465" spans="1:9">
       <c r="A465" s="25" t="s">
         <v>37</v>
       </c>
@@ -18423,7 +18408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:9" hidden="1">
+    <row r="466" spans="1:9">
       <c r="A466" s="24" t="s">
         <v>36</v>
       </c>
@@ -18450,7 +18435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:9" hidden="1">
+    <row r="467" spans="1:9">
       <c r="A467" s="19" t="s">
         <v>79</v>
       </c>
@@ -18479,7 +18464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:9" hidden="1">
+    <row r="468" spans="1:9">
       <c r="A468" s="24" t="s">
         <v>80</v>
       </c>
@@ -18506,7 +18491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:9" hidden="1">
+    <row r="469" spans="1:9">
       <c r="A469" s="19" t="s">
         <v>51</v>
       </c>
@@ -18535,7 +18520,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="470" spans="1:9" hidden="1">
+    <row r="470" spans="1:9">
       <c r="A470" s="24" t="s">
         <v>70</v>
       </c>
@@ -18562,7 +18547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:9" hidden="1">
+    <row r="471" spans="1:9">
       <c r="A471" s="25" t="s">
         <v>33</v>
       </c>
@@ -18589,7 +18574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:9" hidden="1">
+    <row r="472" spans="1:9">
       <c r="A472" s="26" t="s">
         <v>1123</v>
       </c>
@@ -18612,13 +18597,13 @@
         <v>148</v>
       </c>
       <c r="H472" s="6" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="I472" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:9" hidden="1">
+    <row r="473" spans="1:9">
       <c r="A473" s="23" t="s">
         <v>1121</v>
       </c>
@@ -18647,7 +18632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:9" hidden="1">
+    <row r="474" spans="1:9">
       <c r="A474" s="24" t="s">
         <v>52</v>
       </c>
@@ -18674,7 +18659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:9" hidden="1">
+    <row r="475" spans="1:9">
       <c r="A475" s="23" t="s">
         <v>1094</v>
       </c>
@@ -18908,7 +18893,7 @@
       <c r="E483" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F483" s="34" t="s">
+      <c r="F483" s="35" t="s">
         <v>1679</v>
       </c>
       <c r="G483" s="9" t="s">
@@ -19288,7 +19273,7 @@
       <c r="E497" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F497" s="34" t="s">
+      <c r="F497" s="35" t="s">
         <v>1679</v>
       </c>
       <c r="G497" s="9" t="s">
@@ -19405,7 +19390,7 @@
         <v>178</v>
       </c>
       <c r="H501" s="9" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="I501" s="7" t="s">
         <v>0</v>
@@ -19465,7 +19450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:9" hidden="1">
+    <row r="504" spans="1:9">
       <c r="A504" s="24" t="s">
         <v>1393</v>
       </c>
@@ -19492,7 +19477,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="505" spans="1:9" hidden="1">
+    <row r="505" spans="1:9">
       <c r="A505" s="25" t="s">
         <v>1391</v>
       </c>
@@ -19519,7 +19504,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="506" spans="1:9" hidden="1">
+    <row r="506" spans="1:9">
       <c r="A506" s="24" t="s">
         <v>1388</v>
       </c>
@@ -19546,7 +19531,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="507" spans="1:9" hidden="1">
+    <row r="507" spans="1:9">
       <c r="A507" s="19" t="s">
         <v>747</v>
       </c>
@@ -19573,7 +19558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:9" hidden="1">
+    <row r="508" spans="1:9">
       <c r="A508" s="22" t="s">
         <v>744</v>
       </c>
@@ -19602,7 +19587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:9" hidden="1">
+    <row r="509" spans="1:9">
       <c r="A509" s="23" t="s">
         <v>863</v>
       </c>
@@ -19631,7 +19616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:9" hidden="1">
+    <row r="510" spans="1:9">
       <c r="A510" s="22" t="s">
         <v>1417</v>
       </c>
@@ -19658,7 +19643,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="511" spans="1:9" hidden="1">
+    <row r="511" spans="1:9">
       <c r="A511" s="19" t="s">
         <v>875</v>
       </c>
@@ -19687,7 +19672,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="512" spans="1:9" hidden="1">
+    <row r="512" spans="1:9">
       <c r="A512" s="22" t="s">
         <v>1249</v>
       </c>
@@ -19714,7 +19699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:9" hidden="1">
+    <row r="513" spans="1:9">
       <c r="A513" s="19" t="s">
         <v>1233</v>
       </c>
@@ -19741,7 +19726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:9" hidden="1">
+    <row r="514" spans="1:9">
       <c r="A514" s="22" t="s">
         <v>873</v>
       </c>
@@ -19768,7 +19753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:9" hidden="1">
+    <row r="515" spans="1:9">
       <c r="A515" s="19" t="s">
         <v>871</v>
       </c>
@@ -19797,7 +19782,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="516" spans="1:9" hidden="1">
+    <row r="516" spans="1:9">
       <c r="A516" s="22" t="s">
         <v>1409</v>
       </c>
@@ -19824,7 +19809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:9" hidden="1">
+    <row r="517" spans="1:9">
       <c r="A517" s="19" t="s">
         <v>869</v>
       </c>
@@ -19851,7 +19836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:9" hidden="1">
+    <row r="518" spans="1:9">
       <c r="A518" s="22" t="s">
         <v>866</v>
       </c>
@@ -19878,7 +19863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:9" hidden="1">
+    <row r="519" spans="1:9">
       <c r="A519" s="19" t="s">
         <v>1108</v>
       </c>
@@ -19905,7 +19890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:9" hidden="1">
+    <row r="520" spans="1:9">
       <c r="A520" s="22" t="s">
         <v>877</v>
       </c>
@@ -19932,7 +19917,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="521" spans="1:9" hidden="1">
+    <row r="521" spans="1:9">
       <c r="A521" s="25" t="s">
         <v>1384</v>
       </c>
@@ -19959,7 +19944,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="522" spans="1:9" hidden="1">
+    <row r="522" spans="1:9">
       <c r="A522" s="24" t="s">
         <v>1382</v>
       </c>
@@ -19986,7 +19971,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="523" spans="1:9" hidden="1">
+    <row r="523" spans="1:9">
       <c r="A523" s="25" t="s">
         <v>1386</v>
       </c>
@@ -20013,7 +19998,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="524" spans="1:9" hidden="1">
+    <row r="524" spans="1:9">
       <c r="A524" s="22" t="s">
         <v>1665</v>
       </c>
@@ -20040,7 +20025,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="525" spans="1:9" hidden="1">
+    <row r="525" spans="1:9">
       <c r="A525" s="19" t="s">
         <v>1660</v>
       </c>
@@ -20067,7 +20052,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="526" spans="1:9" hidden="1">
+    <row r="526" spans="1:9">
       <c r="A526" s="26" t="s">
         <v>1343</v>
       </c>
@@ -20094,7 +20079,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="527" spans="1:9" hidden="1">
+    <row r="527" spans="1:9">
       <c r="A527" s="23" t="s">
         <v>1341</v>
       </c>
@@ -20121,7 +20106,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="528" spans="1:9" hidden="1">
+    <row r="528" spans="1:9">
       <c r="A528" s="26" t="s">
         <v>1345</v>
       </c>
@@ -20148,7 +20133,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="529" spans="1:9" hidden="1">
+    <row r="529" spans="1:9">
       <c r="A529" s="23" t="s">
         <v>1347</v>
       </c>
@@ -20175,7 +20160,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="530" spans="1:9" hidden="1">
+    <row r="530" spans="1:9">
       <c r="A530" s="26" t="s">
         <v>1349</v>
       </c>
@@ -20202,7 +20187,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="531" spans="1:9" hidden="1">
+    <row r="531" spans="1:9">
       <c r="A531" s="23" t="s">
         <v>1351</v>
       </c>
@@ -20229,7 +20214,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="532" spans="1:9" hidden="1">
+    <row r="532" spans="1:9">
       <c r="A532" s="26" t="s">
         <v>1353</v>
       </c>
@@ -20256,7 +20241,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="533" spans="1:9" hidden="1">
+    <row r="533" spans="1:9">
       <c r="A533" s="23" t="s">
         <v>1355</v>
       </c>
@@ -20283,7 +20268,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="534" spans="1:9" hidden="1">
+    <row r="534" spans="1:9">
       <c r="A534" s="24" t="s">
         <v>1357</v>
       </c>
@@ -20310,7 +20295,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="535" spans="1:9" hidden="1">
+    <row r="535" spans="1:9">
       <c r="A535" s="25" t="s">
         <v>1359</v>
       </c>
@@ -20339,7 +20324,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="536" spans="1:9" hidden="1">
+    <row r="536" spans="1:9">
       <c r="A536" s="24" t="s">
         <v>1361</v>
       </c>
@@ -20366,7 +20351,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="537" spans="1:9" hidden="1">
+    <row r="537" spans="1:9">
       <c r="A537" s="23" t="s">
         <v>1338</v>
       </c>
@@ -20393,7 +20378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:9" hidden="1">
+    <row r="538" spans="1:9">
       <c r="A538" s="24" t="s">
         <v>1363</v>
       </c>
@@ -20420,7 +20405,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="539" spans="1:9" hidden="1">
+    <row r="539" spans="1:9">
       <c r="A539" s="25" t="s">
         <v>1377</v>
       </c>
@@ -20447,7 +20432,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="540" spans="1:9" hidden="1">
+    <row r="540" spans="1:9">
       <c r="A540" s="24" t="s">
         <v>1379</v>
       </c>
@@ -20474,7 +20459,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="541" spans="1:9" hidden="1">
+    <row r="541" spans="1:9">
       <c r="A541" s="25" t="s">
         <v>1370</v>
       </c>
@@ -20503,7 +20488,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="542" spans="1:9" hidden="1">
+    <row r="542" spans="1:9">
       <c r="A542" s="24" t="s">
         <v>1380</v>
       </c>
@@ -20530,7 +20515,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="543" spans="1:9" hidden="1">
+    <row r="543" spans="1:9">
       <c r="A543" s="25" t="s">
         <v>1375</v>
       </c>
@@ -20557,7 +20542,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="544" spans="1:9" hidden="1">
+    <row r="544" spans="1:9">
       <c r="A544" s="24" t="s">
         <v>1373</v>
       </c>
@@ -20584,7 +20569,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="545" spans="1:9" hidden="1">
+    <row r="545" spans="1:9">
       <c r="A545" s="23" t="s">
         <v>891</v>
       </c>
@@ -20611,7 +20596,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="546" spans="1:9" hidden="1">
+    <row r="546" spans="1:9">
       <c r="A546" s="26" t="s">
         <v>889</v>
       </c>
@@ -20638,7 +20623,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="547" spans="1:9" hidden="1">
+    <row r="547" spans="1:9">
       <c r="A547" s="23" t="s">
         <v>887</v>
       </c>
@@ -20665,7 +20650,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="548" spans="1:9" hidden="1">
+    <row r="548" spans="1:9">
       <c r="A548" s="26" t="s">
         <v>885</v>
       </c>
@@ -20692,7 +20677,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="549" spans="1:9" hidden="1">
+    <row r="549" spans="1:9">
       <c r="A549" s="23" t="s">
         <v>883</v>
       </c>
@@ -20719,7 +20704,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="550" spans="1:9" hidden="1">
+    <row r="550" spans="1:9">
       <c r="A550" s="26" t="s">
         <v>880</v>
       </c>
@@ -20748,7 +20733,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="551" spans="1:9" hidden="1">
+    <row r="551" spans="1:9">
       <c r="A551" s="19" t="s">
         <v>1331</v>
       </c>
@@ -20775,7 +20760,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="552" spans="1:9" hidden="1">
+    <row r="552" spans="1:9">
       <c r="A552" s="22" t="s">
         <v>1606</v>
       </c>
@@ -20802,7 +20787,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="553" spans="1:9" hidden="1">
+    <row r="553" spans="1:9">
       <c r="A553" s="19" t="s">
         <v>1336</v>
       </c>
@@ -20829,7 +20814,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="554" spans="1:9" ht="15.75" hidden="1">
+    <row r="554" spans="1:9" ht="15.75">
       <c r="A554" s="53" t="s">
         <v>1334</v>
       </c>
@@ -20856,7 +20841,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="555" spans="1:9" hidden="1">
+    <row r="555" spans="1:9">
       <c r="A555" s="19" t="s">
         <v>1610</v>
       </c>
@@ -20881,7 +20866,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="556" spans="1:9" hidden="1">
+    <row r="556" spans="1:9">
       <c r="A556" s="22" t="s">
         <v>1087</v>
       </c>
@@ -20906,7 +20891,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="557" spans="1:9" hidden="1">
+    <row r="557" spans="1:9">
       <c r="A557" s="19" t="s">
         <v>1085</v>
       </c>
@@ -20931,7 +20916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:9" hidden="1">
+    <row r="558" spans="1:9">
       <c r="A558" s="22" t="s">
         <v>1083</v>
       </c>
@@ -20956,7 +20941,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="559" spans="1:9" hidden="1">
+    <row r="559" spans="1:9">
       <c r="A559" s="23" t="s">
         <v>1081</v>
       </c>
@@ -20981,7 +20966,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="560" spans="1:9" hidden="1">
+    <row r="560" spans="1:9">
       <c r="A560" s="22" t="s">
         <v>1079</v>
       </c>
@@ -21006,7 +20991,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="561" spans="1:9" hidden="1">
+    <row r="561" spans="1:9">
       <c r="A561" s="23" t="s">
         <v>1077</v>
       </c>
@@ -21033,7 +21018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="562" spans="1:9" hidden="1">
+    <row r="562" spans="1:9">
       <c r="A562" s="26" t="s">
         <v>1075</v>
       </c>
@@ -21058,7 +21043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="563" spans="1:9" hidden="1">
+    <row r="563" spans="1:9">
       <c r="A563" s="19" t="s">
         <v>1073</v>
       </c>
@@ -21083,7 +21068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:9" hidden="1">
+    <row r="564" spans="1:9">
       <c r="A564" s="22" t="s">
         <v>1071</v>
       </c>
@@ -21110,7 +21095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:9" hidden="1">
+    <row r="565" spans="1:9">
       <c r="A565" s="23" t="s">
         <v>1069</v>
       </c>
@@ -21137,7 +21122,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="566" spans="1:9" hidden="1">
+    <row r="566" spans="1:9">
       <c r="A566" s="22" t="s">
         <v>1067</v>
       </c>
@@ -21162,7 +21147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:9" hidden="1">
+    <row r="567" spans="1:9">
       <c r="A567" s="19" t="s">
         <v>1065</v>
       </c>
@@ -21187,7 +21172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:9" hidden="1">
+    <row r="568" spans="1:9">
       <c r="A568" s="22" t="s">
         <v>1063</v>
       </c>
@@ -21212,7 +21197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:9" hidden="1">
+    <row r="569" spans="1:9">
       <c r="A569" s="19" t="s">
         <v>1061</v>
       </c>
@@ -21237,7 +21222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:9" hidden="1">
+    <row r="570" spans="1:9">
       <c r="A570" s="22" t="s">
         <v>1059</v>
       </c>
@@ -21262,7 +21247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="1:9" hidden="1">
+    <row r="571" spans="1:9">
       <c r="A571" s="19" t="s">
         <v>1057</v>
       </c>
@@ -21287,7 +21272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:9" hidden="1">
+    <row r="572" spans="1:9">
       <c r="A572" s="26" t="s">
         <v>1055</v>
       </c>
@@ -21312,7 +21297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:9" hidden="1">
+    <row r="573" spans="1:9">
       <c r="A573" s="19" t="s">
         <v>1053</v>
       </c>
@@ -21337,7 +21322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:9" hidden="1">
+    <row r="574" spans="1:9">
       <c r="A574" s="26" t="s">
         <v>1051</v>
       </c>
@@ -21362,7 +21347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:9" hidden="1">
+    <row r="575" spans="1:9">
       <c r="A575" s="19" t="s">
         <v>1049</v>
       </c>
@@ -21387,7 +21372,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="576" spans="1:9" hidden="1">
+    <row r="576" spans="1:9">
       <c r="A576" s="22" t="s">
         <v>1048</v>
       </c>
@@ -21412,7 +21397,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="577" spans="1:9" hidden="1">
+    <row r="577" spans="1:9">
       <c r="A577" s="23" t="s">
         <v>1046</v>
       </c>
@@ -21439,7 +21424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="1:9" hidden="1">
+    <row r="578" spans="1:9">
       <c r="A578" s="22" t="s">
         <v>1044</v>
       </c>
@@ -21464,7 +21449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:9" hidden="1">
+    <row r="579" spans="1:9">
       <c r="A579" s="19" t="s">
         <v>1042</v>
       </c>
@@ -21489,7 +21474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="580" spans="1:9" hidden="1">
+    <row r="580" spans="1:9">
       <c r="A580" s="22" t="s">
         <v>1040</v>
       </c>
@@ -21514,7 +21499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:9" hidden="1">
+    <row r="581" spans="1:9">
       <c r="A581" s="19" t="s">
         <v>1038</v>
       </c>
@@ -21539,7 +21524,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="582" spans="1:9" hidden="1">
+    <row r="582" spans="1:9">
       <c r="A582" s="22" t="s">
         <v>1036</v>
       </c>
@@ -21564,7 +21549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="583" spans="1:9" hidden="1">
+    <row r="583" spans="1:9">
       <c r="A583" s="19" t="s">
         <v>1034</v>
       </c>
@@ -21589,7 +21574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:9" hidden="1">
+    <row r="584" spans="1:9">
       <c r="A584" s="22" t="s">
         <v>1032</v>
       </c>
@@ -21614,7 +21599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:9" hidden="1">
+    <row r="585" spans="1:9">
       <c r="A585" s="19" t="s">
         <v>1030</v>
       </c>
@@ -21639,7 +21624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:9" hidden="1">
+    <row r="586" spans="1:9">
       <c r="A586" s="26" t="s">
         <v>1028</v>
       </c>
@@ -21664,7 +21649,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="587" spans="1:9" hidden="1">
+    <row r="587" spans="1:9">
       <c r="A587" s="19" t="s">
         <v>1026</v>
       </c>
@@ -21689,7 +21674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:9" hidden="1">
+    <row r="588" spans="1:9">
       <c r="A588" s="22" t="s">
         <v>1024</v>
       </c>
@@ -21714,7 +21699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:9" hidden="1">
+    <row r="589" spans="1:9">
       <c r="A589" s="19" t="s">
         <v>1022</v>
       </c>
@@ -21739,7 +21724,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="590" spans="1:9" hidden="1">
+    <row r="590" spans="1:9">
       <c r="A590" s="22" t="s">
         <v>1020</v>
       </c>
@@ -21764,7 +21749,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="591" spans="1:9" hidden="1">
+    <row r="591" spans="1:9">
       <c r="A591" s="19" t="s">
         <v>1018</v>
       </c>
@@ -21789,7 +21774,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="592" spans="1:9" hidden="1">
+    <row r="592" spans="1:9">
       <c r="A592" s="22" t="s">
         <v>1016</v>
       </c>
@@ -21816,7 +21801,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="593" spans="1:9" hidden="1">
+    <row r="593" spans="1:9">
       <c r="A593" s="19" t="s">
         <v>1014</v>
       </c>
@@ -21841,7 +21826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="594" spans="1:9" hidden="1">
+    <row r="594" spans="1:9">
       <c r="A594" s="22" t="s">
         <v>1012</v>
       </c>
@@ -21866,7 +21851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:9" hidden="1">
+    <row r="595" spans="1:9">
       <c r="A595" s="19" t="s">
         <v>1010</v>
       </c>
@@ -21891,7 +21876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:9" hidden="1">
+    <row r="596" spans="1:9">
       <c r="A596" s="22" t="s">
         <v>1008</v>
       </c>
@@ -21916,7 +21901,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="597" spans="1:9" hidden="1">
+    <row r="597" spans="1:9">
       <c r="A597" s="19" t="s">
         <v>1006</v>
       </c>
@@ -21941,7 +21926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:9" hidden="1">
+    <row r="598" spans="1:9">
       <c r="A598" s="22" t="s">
         <v>1004</v>
       </c>
@@ -21966,7 +21951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="599" spans="1:9" hidden="1">
+    <row r="599" spans="1:9">
       <c r="A599" s="19" t="s">
         <v>1002</v>
       </c>
@@ -21991,7 +21976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="600" spans="1:9" hidden="1">
+    <row r="600" spans="1:9">
       <c r="A600" s="22" t="s">
         <v>1000</v>
       </c>
@@ -22016,7 +22001,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="601" spans="1:9" hidden="1">
+    <row r="601" spans="1:9">
       <c r="A601" s="19" t="s">
         <v>998</v>
       </c>
@@ -22043,7 +22028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:9" hidden="1">
+    <row r="602" spans="1:9">
       <c r="A602" s="22" t="s">
         <v>996</v>
       </c>
@@ -22068,7 +22053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:9" hidden="1">
+    <row r="603" spans="1:9">
       <c r="A603" s="19" t="s">
         <v>994</v>
       </c>
@@ -22093,7 +22078,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="604" spans="1:9" hidden="1">
+    <row r="604" spans="1:9">
       <c r="A604" s="22" t="s">
         <v>992</v>
       </c>
@@ -22118,7 +22103,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="605" spans="1:9" hidden="1">
+    <row r="605" spans="1:9">
       <c r="A605" s="19" t="s">
         <v>990</v>
       </c>
@@ -22143,7 +22128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:9" hidden="1">
+    <row r="606" spans="1:9">
       <c r="A606" s="22" t="s">
         <v>988</v>
       </c>
@@ -22168,7 +22153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="607" spans="1:9" hidden="1">
+    <row r="607" spans="1:9">
       <c r="A607" s="19" t="s">
         <v>986</v>
       </c>
@@ -22193,7 +22178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:9" hidden="1">
+    <row r="608" spans="1:9">
       <c r="A608" s="26" t="s">
         <v>984</v>
       </c>
@@ -22218,7 +22203,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="609" spans="1:9" hidden="1">
+    <row r="609" spans="1:9">
       <c r="A609" s="19" t="s">
         <v>982</v>
       </c>
@@ -22243,7 +22228,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="610" spans="1:9" hidden="1">
+    <row r="610" spans="1:9">
       <c r="A610" s="22" t="s">
         <v>980</v>
       </c>
@@ -22268,7 +22253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:9" hidden="1">
+    <row r="611" spans="1:9">
       <c r="A611" s="19" t="s">
         <v>978</v>
       </c>
@@ -22293,7 +22278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:9" hidden="1">
+    <row r="612" spans="1:9">
       <c r="A612" s="22" t="s">
         <v>976</v>
       </c>
@@ -22318,7 +22303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="613" spans="1:9" hidden="1">
+    <row r="613" spans="1:9">
       <c r="A613" s="19" t="s">
         <v>974</v>
       </c>
@@ -22343,7 +22328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="1:9" hidden="1">
+    <row r="614" spans="1:9">
       <c r="A614" s="22" t="s">
         <v>972</v>
       </c>
@@ -22370,7 +22355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="615" spans="1:9" hidden="1">
+    <row r="615" spans="1:9">
       <c r="A615" s="19" t="s">
         <v>970</v>
       </c>
@@ -22395,7 +22380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:9" hidden="1">
+    <row r="616" spans="1:9">
       <c r="A616" s="22" t="s">
         <v>968</v>
       </c>
@@ -22420,7 +22405,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="617" spans="1:9" hidden="1">
+    <row r="617" spans="1:9">
       <c r="A617" s="19" t="s">
         <v>966</v>
       </c>
@@ -22445,7 +22430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="618" spans="1:9" hidden="1">
+    <row r="618" spans="1:9">
       <c r="A618" s="22" t="s">
         <v>964</v>
       </c>
@@ -22470,7 +22455,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="619" spans="1:9" hidden="1">
+    <row r="619" spans="1:9">
       <c r="A619" s="19" t="s">
         <v>962</v>
       </c>
@@ -22497,7 +22482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="620" spans="1:9" hidden="1">
+    <row r="620" spans="1:9">
       <c r="A620" s="22" t="s">
         <v>960</v>
       </c>
@@ -22522,7 +22507,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="621" spans="1:9" hidden="1">
+    <row r="621" spans="1:9">
       <c r="A621" s="19" t="s">
         <v>958</v>
       </c>
@@ -22549,7 +22534,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="622" spans="1:9" hidden="1">
+    <row r="622" spans="1:9">
       <c r="A622" s="22" t="s">
         <v>956</v>
       </c>
@@ -22574,7 +22559,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="623" spans="1:9" hidden="1">
+    <row r="623" spans="1:9">
       <c r="A623" s="23" t="s">
         <v>954</v>
       </c>
@@ -22599,7 +22584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="624" spans="1:9" hidden="1">
+    <row r="624" spans="1:9">
       <c r="A624" s="22" t="s">
         <v>951</v>
       </c>
@@ -22624,7 +22609,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="625" spans="1:9" hidden="1">
+    <row r="625" spans="1:9">
       <c r="A625" s="19" t="s">
         <v>949</v>
       </c>
@@ -22649,7 +22634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:9" hidden="1">
+    <row r="626" spans="1:9">
       <c r="A626" s="22" t="s">
         <v>947</v>
       </c>
@@ -22674,7 +22659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:9" hidden="1">
+    <row r="627" spans="1:9">
       <c r="A627" s="19" t="s">
         <v>945</v>
       </c>
@@ -22699,7 +22684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="628" spans="1:9" hidden="1">
+    <row r="628" spans="1:9">
       <c r="A628" s="22" t="s">
         <v>943</v>
       </c>
@@ -22724,7 +22709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:9" hidden="1">
+    <row r="629" spans="1:9">
       <c r="A629" s="19" t="s">
         <v>941</v>
       </c>
@@ -22749,7 +22734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:9" hidden="1">
+    <row r="630" spans="1:9">
       <c r="A630" s="22" t="s">
         <v>939</v>
       </c>
@@ -22774,7 +22759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:9" hidden="1">
+    <row r="631" spans="1:9">
       <c r="A631" s="47" t="s">
         <v>936</v>
       </c>
@@ -22799,7 +22784,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="632" spans="1:9" hidden="1">
+    <row r="632" spans="1:9">
       <c r="A632" s="50" t="s">
         <v>933</v>
       </c>
@@ -22824,7 +22809,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="633" spans="1:9" hidden="1">
+    <row r="633" spans="1:9">
       <c r="A633" s="51" t="s">
         <v>931</v>
       </c>
@@ -22849,7 +22834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:9" hidden="1">
+    <row r="634" spans="1:9">
       <c r="A634" s="49" t="s">
         <v>929</v>
       </c>
@@ -22874,7 +22859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="635" spans="1:9" hidden="1">
+    <row r="635" spans="1:9">
       <c r="A635" s="47" t="s">
         <v>927</v>
       </c>
@@ -22899,7 +22884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:9" hidden="1">
+    <row r="636" spans="1:9">
       <c r="A636" s="50" t="s">
         <v>925</v>
       </c>
@@ -22924,7 +22909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="637" spans="1:9" hidden="1">
+    <row r="637" spans="1:9">
       <c r="A637" s="47" t="s">
         <v>922</v>
       </c>
@@ -22949,7 +22934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="638" spans="1:9" hidden="1">
+    <row r="638" spans="1:9">
       <c r="A638" s="49" t="s">
         <v>919</v>
       </c>
@@ -22974,7 +22959,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="639" spans="1:9" hidden="1">
+    <row r="639" spans="1:9">
       <c r="A639" s="51" t="s">
         <v>917</v>
       </c>
@@ -22999,7 +22984,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="640" spans="1:9" hidden="1">
+    <row r="640" spans="1:9">
       <c r="A640" s="49" t="s">
         <v>915</v>
       </c>
@@ -23024,7 +23009,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="641" spans="1:9" hidden="1">
+    <row r="641" spans="1:9">
       <c r="A641" s="19" t="s">
         <v>913</v>
       </c>
@@ -23049,7 +23034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:9" hidden="1">
+    <row r="642" spans="1:9">
       <c r="A642" s="22" t="s">
         <v>911</v>
       </c>
@@ -23074,7 +23059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:9" hidden="1">
+    <row r="643" spans="1:9">
       <c r="A643" s="19" t="s">
         <v>909</v>
       </c>
@@ -23099,7 +23084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:9" hidden="1">
+    <row r="644" spans="1:9">
       <c r="A644" s="22" t="s">
         <v>907</v>
       </c>
@@ -23124,7 +23109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="645" spans="1:9" hidden="1">
+    <row r="645" spans="1:9">
       <c r="A645" s="19" t="s">
         <v>905</v>
       </c>
@@ -23151,7 +23136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:9" hidden="1">
+    <row r="646" spans="1:9">
       <c r="A646" s="26" t="s">
         <v>903</v>
       </c>
@@ -23176,7 +23161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="647" spans="1:9" hidden="1">
+    <row r="647" spans="1:9">
       <c r="A647" s="19" t="s">
         <v>901</v>
       </c>
@@ -23203,7 +23188,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="648" spans="1:9" hidden="1">
+    <row r="648" spans="1:9">
       <c r="A648" s="26" t="s">
         <v>899</v>
       </c>
@@ -23230,7 +23215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="649" spans="1:9" hidden="1">
+    <row r="649" spans="1:9">
       <c r="A649" s="19" t="s">
         <v>896</v>
       </c>
@@ -23255,7 +23240,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="650" spans="1:9" hidden="1">
+    <row r="650" spans="1:9">
       <c r="A650" s="22" t="s">
         <v>893</v>
       </c>
@@ -23280,7 +23265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="651" spans="1:9" hidden="1">
+    <row r="651" spans="1:9">
       <c r="A651" s="19" t="s">
         <v>571</v>
       </c>
@@ -23305,7 +23290,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="652" spans="1:9" hidden="1">
+    <row r="652" spans="1:9">
       <c r="A652" s="26" t="s">
         <v>1291</v>
       </c>
@@ -23330,7 +23315,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="653" spans="1:9" hidden="1">
+    <row r="653" spans="1:9">
       <c r="A653" s="23" t="s">
         <v>1289</v>
       </c>
@@ -23355,7 +23340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:9" hidden="1">
+    <row r="654" spans="1:9">
       <c r="A654" s="22" t="s">
         <v>1287</v>
       </c>
@@ -23380,7 +23365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:9" hidden="1">
+    <row r="655" spans="1:9">
       <c r="A655" s="19" t="s">
         <v>1625</v>
       </c>
@@ -23405,7 +23390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:9" hidden="1">
+    <row r="656" spans="1:9">
       <c r="A656" s="22" t="s">
         <v>609</v>
       </c>
@@ -23432,7 +23417,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="657" spans="1:9" hidden="1">
+    <row r="657" spans="1:9">
       <c r="A657" s="19" t="s">
         <v>1284</v>
       </c>
@@ -23457,7 +23442,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="658" spans="1:9" hidden="1">
+    <row r="658" spans="1:9">
       <c r="A658" s="22" t="s">
         <v>1282</v>
       </c>
@@ -23482,7 +23467,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="659" spans="1:9" hidden="1">
+    <row r="659" spans="1:9">
       <c r="A659" s="23" t="s">
         <v>606</v>
       </c>
@@ -23507,7 +23492,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="660" spans="1:9" hidden="1">
+    <row r="660" spans="1:9">
       <c r="A660" s="26" t="s">
         <v>1280</v>
       </c>
@@ -23532,7 +23517,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="661" spans="1:9" hidden="1">
+    <row r="661" spans="1:9">
       <c r="A661" s="19" t="s">
         <v>1278</v>
       </c>
@@ -23557,7 +23542,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="662" spans="1:9" hidden="1">
+    <row r="662" spans="1:9">
       <c r="A662" s="22" t="s">
         <v>1276</v>
       </c>
@@ -23582,7 +23567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:9" hidden="1">
+    <row r="663" spans="1:9">
       <c r="A663" s="23" t="s">
         <v>189</v>
       </c>
@@ -23607,7 +23592,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="664" spans="1:9" hidden="1">
+    <row r="664" spans="1:9">
       <c r="A664" s="22" t="s">
         <v>1629</v>
       </c>
@@ -23634,7 +23619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:9" hidden="1">
+    <row r="665" spans="1:9">
       <c r="A665" s="19" t="s">
         <v>544</v>
       </c>
@@ -23659,7 +23644,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="666" spans="1:9" hidden="1">
+    <row r="666" spans="1:9">
       <c r="A666" s="22" t="s">
         <v>1271</v>
       </c>
@@ -23684,7 +23669,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="667" spans="1:9" hidden="1">
+    <row r="667" spans="1:9">
       <c r="A667" s="19" t="s">
         <v>1269</v>
       </c>
@@ -23709,7 +23694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="668" spans="1:9" hidden="1">
+    <row r="668" spans="1:9">
       <c r="A668" s="22" t="s">
         <v>1267</v>
       </c>
@@ -23734,7 +23719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:9" hidden="1">
+    <row r="669" spans="1:9">
       <c r="A669" s="23" t="s">
         <v>740</v>
       </c>
@@ -23759,7 +23744,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="670" spans="1:9" hidden="1">
+    <row r="670" spans="1:9">
       <c r="A670" s="26" t="s">
         <v>569</v>
       </c>
@@ -23784,7 +23769,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="671" spans="1:9" hidden="1">
+    <row r="671" spans="1:9">
       <c r="A671" s="19" t="s">
         <v>1261</v>
       </c>
@@ -23809,7 +23794,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="672" spans="1:9" hidden="1">
+    <row r="672" spans="1:9">
       <c r="A672" s="22" t="s">
         <v>567</v>
       </c>
@@ -23834,7 +23819,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="673" spans="1:9" hidden="1">
+    <row r="673" spans="1:9">
       <c r="A673" s="19" t="s">
         <v>1257</v>
       </c>
@@ -23859,7 +23844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:9" hidden="1">
+    <row r="674" spans="1:9">
       <c r="A674" s="22" t="s">
         <v>1255</v>
       </c>
@@ -23884,7 +23869,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="675" spans="1:9" hidden="1">
+    <row r="675" spans="1:9">
       <c r="A675" s="23" t="s">
         <v>1253</v>
       </c>
@@ -23911,7 +23896,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="676" spans="1:9" hidden="1">
+    <row r="676" spans="1:9">
       <c r="A676" s="26" t="s">
         <v>1251</v>
       </c>
@@ -23936,7 +23921,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="677" spans="1:9" hidden="1">
+    <row r="677" spans="1:9">
       <c r="A677" s="19" t="s">
         <v>1247</v>
       </c>
@@ -23961,7 +23946,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="678" spans="1:9" hidden="1">
+    <row r="678" spans="1:9">
       <c r="A678" s="22" t="s">
         <v>1245</v>
       </c>
@@ -23986,7 +23971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:9" hidden="1">
+    <row r="679" spans="1:9">
       <c r="A679" s="23" t="s">
         <v>542</v>
       </c>
@@ -24011,7 +23996,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="680" spans="1:9" hidden="1">
+    <row r="680" spans="1:9">
       <c r="A680" s="22" t="s">
         <v>540</v>
       </c>
@@ -24036,7 +24021,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="681" spans="1:9" hidden="1">
+    <row r="681" spans="1:9">
       <c r="A681" s="19" t="s">
         <v>1243</v>
       </c>
@@ -24061,7 +24046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:9" hidden="1">
+    <row r="682" spans="1:9">
       <c r="A682" s="26" t="s">
         <v>1241</v>
       </c>
@@ -24088,7 +24073,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="683" spans="1:9" hidden="1">
+    <row r="683" spans="1:9">
       <c r="A683" s="19" t="s">
         <v>1239</v>
       </c>
@@ -24113,7 +24098,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="684" spans="1:9" hidden="1">
+    <row r="684" spans="1:9">
       <c r="A684" s="26" t="s">
         <v>596</v>
       </c>
@@ -24138,7 +24123,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="685" spans="1:9" hidden="1">
+    <row r="685" spans="1:9">
       <c r="A685" s="19" t="s">
         <v>1237</v>
       </c>
@@ -24163,7 +24148,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="686" spans="1:9" hidden="1">
+    <row r="686" spans="1:9">
       <c r="A686" s="22" t="s">
         <v>1235</v>
       </c>
@@ -24188,7 +24173,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="687" spans="1:9" hidden="1">
+    <row r="687" spans="1:9">
       <c r="A687" s="19" t="s">
         <v>1231</v>
       </c>
@@ -24213,7 +24198,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="688" spans="1:9" hidden="1">
+    <row r="688" spans="1:9">
       <c r="A688" s="22" t="s">
         <v>1227</v>
       </c>
@@ -24236,7 +24221,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="689" spans="1:9" hidden="1">
+    <row r="689" spans="1:9">
       <c r="A689" s="19" t="s">
         <v>1225</v>
       </c>
@@ -24263,7 +24248,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="690" spans="1:9" hidden="1">
+    <row r="690" spans="1:9">
       <c r="A690" s="22" t="s">
         <v>1223</v>
       </c>
@@ -24288,7 +24273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:9" hidden="1">
+    <row r="691" spans="1:9">
       <c r="A691" s="23" t="s">
         <v>733</v>
       </c>
@@ -24313,7 +24298,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="692" spans="1:9" hidden="1">
+    <row r="692" spans="1:9">
       <c r="A692" s="22" t="s">
         <v>1219</v>
       </c>
@@ -24338,7 +24323,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="693" spans="1:9" hidden="1">
+    <row r="693" spans="1:9">
       <c r="A693" s="23" t="s">
         <v>68</v>
       </c>
@@ -24365,7 +24350,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="694" spans="1:9" hidden="1">
+    <row r="694" spans="1:9">
       <c r="A694" s="26" t="s">
         <v>536</v>
       </c>
@@ -24417,7 +24402,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="696" spans="1:9" hidden="1">
+    <row r="696" spans="1:9">
       <c r="A696" s="22" t="s">
         <v>1214</v>
       </c>
@@ -24442,7 +24427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="697" spans="1:9" hidden="1">
+    <row r="697" spans="1:9">
       <c r="A697" s="19" t="s">
         <v>1212</v>
       </c>
@@ -24469,7 +24454,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="698" spans="1:9" hidden="1">
+    <row r="698" spans="1:9">
       <c r="A698" s="22" t="s">
         <v>1210</v>
       </c>
@@ -24494,7 +24479,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="699" spans="1:9" hidden="1">
+    <row r="699" spans="1:9">
       <c r="A699" s="23" t="s">
         <v>565</v>
       </c>
@@ -24519,7 +24504,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="700" spans="1:9" hidden="1">
+    <row r="700" spans="1:9">
       <c r="A700" s="22" t="s">
         <v>119</v>
       </c>
@@ -24544,7 +24529,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="701" spans="1:9" hidden="1">
+    <row r="701" spans="1:9">
       <c r="A701" s="19" t="s">
         <v>118</v>
       </c>
@@ -24569,7 +24554,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="702" spans="1:9" hidden="1">
+    <row r="702" spans="1:9">
       <c r="A702" s="22" t="s">
         <v>113</v>
       </c>
@@ -24594,7 +24579,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="703" spans="1:9" hidden="1">
+    <row r="703" spans="1:9">
       <c r="A703" s="19" t="s">
         <v>534</v>
       </c>
@@ -24621,7 +24606,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="704" spans="1:9" hidden="1">
+    <row r="704" spans="1:9">
       <c r="A704" s="22" t="s">
         <v>588</v>
       </c>
@@ -24646,7 +24631,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="705" spans="1:9" hidden="1">
+    <row r="705" spans="1:9">
       <c r="A705" s="23" t="s">
         <v>181</v>
       </c>
@@ -24671,7 +24656,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="706" spans="1:9" hidden="1">
+    <row r="706" spans="1:9">
       <c r="A706" s="22" t="s">
         <v>531</v>
       </c>
@@ -24696,7 +24681,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="707" spans="1:9" hidden="1">
+    <row r="707" spans="1:9">
       <c r="A707" s="23" t="s">
         <v>1206</v>
       </c>
@@ -24723,7 +24708,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="708" spans="1:9" hidden="1">
+    <row r="708" spans="1:9">
       <c r="A708" s="26" t="s">
         <v>1204</v>
       </c>
@@ -24748,7 +24733,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="709" spans="1:9" hidden="1">
+    <row r="709" spans="1:9">
       <c r="A709" s="23" t="s">
         <v>1202</v>
       </c>
@@ -24773,7 +24758,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="710" spans="1:9" hidden="1">
+    <row r="710" spans="1:9">
       <c r="A710" s="22" t="s">
         <v>1200</v>
       </c>
@@ -24798,7 +24783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:9" hidden="1">
+    <row r="711" spans="1:9">
       <c r="A711" s="19" t="s">
         <v>529</v>
       </c>
@@ -24823,7 +24808,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="712" spans="1:9" hidden="1">
+    <row r="712" spans="1:9">
       <c r="A712" s="26" t="s">
         <v>1198</v>
       </c>
@@ -24850,7 +24835,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="713" spans="1:9" hidden="1">
+    <row r="713" spans="1:9">
       <c r="A713" s="23" t="s">
         <v>1196</v>
       </c>
@@ -24875,7 +24860,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="714" spans="1:9" hidden="1">
+    <row r="714" spans="1:9">
       <c r="A714" s="22" t="s">
         <v>1194</v>
       </c>
@@ -24900,7 +24885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:9" hidden="1">
+    <row r="715" spans="1:9">
       <c r="A715" s="19" t="s">
         <v>176</v>
       </c>
@@ -24927,7 +24912,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="716" spans="1:9" hidden="1">
+    <row r="716" spans="1:9">
       <c r="A716" s="26" t="s">
         <v>1190</v>
       </c>
@@ -24952,7 +24937,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="717" spans="1:9" hidden="1">
+    <row r="717" spans="1:9">
       <c r="A717" s="19" t="s">
         <v>1188</v>
       </c>
@@ -24977,7 +24962,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="718" spans="1:9" hidden="1">
+    <row r="718" spans="1:9">
       <c r="A718" s="22" t="s">
         <v>585</v>
       </c>
@@ -25002,7 +24987,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="719" spans="1:9" hidden="1">
+    <row r="719" spans="1:9">
       <c r="A719" s="19" t="s">
         <v>49</v>
       </c>
@@ -25029,7 +25014,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="720" spans="1:9" hidden="1">
+    <row r="720" spans="1:9">
       <c r="A720" s="22" t="s">
         <v>1186</v>
       </c>
@@ -25054,7 +25039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="721" spans="1:9" hidden="1">
+    <row r="721" spans="1:9">
       <c r="A721" s="19" t="s">
         <v>1184</v>
       </c>
@@ -25079,7 +25064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="722" spans="1:9" hidden="1">
+    <row r="722" spans="1:9">
       <c r="A722" s="22" t="s">
         <v>563</v>
       </c>
@@ -25102,7 +25087,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="723" spans="1:9" hidden="1">
+    <row r="723" spans="1:9">
       <c r="A723" s="19" t="s">
         <v>1182</v>
       </c>
@@ -25125,7 +25110,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="724" spans="1:9" hidden="1">
+    <row r="724" spans="1:9">
       <c r="A724" s="22" t="s">
         <v>1180</v>
       </c>
@@ -25148,7 +25133,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="725" spans="1:9" hidden="1">
+    <row r="725" spans="1:9">
       <c r="A725" s="19" t="s">
         <v>1178</v>
       </c>
@@ -25173,7 +25158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="726" spans="1:9" hidden="1">
+    <row r="726" spans="1:9">
       <c r="A726" s="26" t="s">
         <v>167</v>
       </c>
@@ -25196,7 +25181,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="727" spans="1:9" hidden="1">
+    <row r="727" spans="1:9">
       <c r="A727" s="19" t="s">
         <v>1176</v>
       </c>
@@ -25221,7 +25206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="728" spans="1:9" hidden="1">
+    <row r="728" spans="1:9">
       <c r="A728" s="22" t="s">
         <v>1631</v>
       </c>
@@ -25244,7 +25229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="729" spans="1:9" hidden="1">
+    <row r="729" spans="1:9">
       <c r="A729" s="19" t="s">
         <v>1172</v>
       </c>
@@ -25269,7 +25254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="730" spans="1:9" hidden="1">
+    <row r="730" spans="1:9">
       <c r="A730" s="22" t="s">
         <v>527</v>
       </c>
@@ -25294,7 +25279,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="731" spans="1:9" hidden="1">
+    <row r="731" spans="1:9">
       <c r="A731" s="23" t="s">
         <v>721</v>
       </c>
@@ -25317,7 +25302,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="732" spans="1:9" hidden="1">
+    <row r="732" spans="1:9">
       <c r="A732" s="22" t="s">
         <v>524</v>
       </c>
@@ -25342,7 +25327,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="733" spans="1:9" hidden="1">
+    <row r="733" spans="1:9">
       <c r="A733" s="19" t="s">
         <v>522</v>
       </c>
@@ -25367,7 +25352,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="734" spans="1:9" hidden="1">
+    <row r="734" spans="1:9">
       <c r="A734" s="22" t="s">
         <v>1168</v>
       </c>
@@ -25392,7 +25377,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="735" spans="1:9" ht="15.75" hidden="1">
+    <row r="735" spans="1:9" ht="15.75">
       <c r="A735" s="19" t="s">
         <v>1166</v>
       </c>
@@ -25419,7 +25404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="736" spans="1:9" hidden="1">
+    <row r="736" spans="1:9">
       <c r="A736" s="22" t="s">
         <v>1164</v>
       </c>
@@ -25442,7 +25427,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="737" spans="1:9" hidden="1">
+    <row r="737" spans="1:9">
       <c r="A737" s="23" t="s">
         <v>165</v>
       </c>
@@ -25465,7 +25450,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="738" spans="1:9" hidden="1">
+    <row r="738" spans="1:9">
       <c r="A738" s="22" t="s">
         <v>518</v>
       </c>
@@ -25488,7 +25473,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="739" spans="1:9" hidden="1">
+    <row r="739" spans="1:9">
       <c r="A739" s="23" t="s">
         <v>1162</v>
       </c>
@@ -25511,7 +25496,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="740" spans="1:9" hidden="1">
+    <row r="740" spans="1:9">
       <c r="A740" s="22" t="s">
         <v>1160</v>
       </c>
@@ -25536,7 +25521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="741" spans="1:9" hidden="1">
+    <row r="741" spans="1:9">
       <c r="A741" s="23" t="s">
         <v>1158</v>
       </c>
@@ -25559,7 +25544,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="742" spans="1:9" hidden="1">
+    <row r="742" spans="1:9">
       <c r="A742" s="22" t="s">
         <v>1156</v>
       </c>
@@ -25582,7 +25567,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="743" spans="1:9" hidden="1">
+    <row r="743" spans="1:9">
       <c r="A743" s="23" t="s">
         <v>159</v>
       </c>
@@ -25605,7 +25590,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="744" spans="1:9" hidden="1">
+    <row r="744" spans="1:9">
       <c r="A744" s="22" t="s">
         <v>1154</v>
       </c>
@@ -25630,7 +25615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="745" spans="1:9" hidden="1">
+    <row r="745" spans="1:9">
       <c r="A745" s="19" t="s">
         <v>1152</v>
       </c>
@@ -25653,7 +25638,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="746" spans="1:9" hidden="1">
+    <row r="746" spans="1:9">
       <c r="A746" s="22" t="s">
         <v>561</v>
       </c>
@@ -25676,7 +25661,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="747" spans="1:9" hidden="1">
+    <row r="747" spans="1:9">
       <c r="A747" s="19" t="s">
         <v>1150</v>
       </c>
@@ -25699,7 +25684,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="748" spans="1:9" hidden="1">
+    <row r="748" spans="1:9">
       <c r="A748" s="29" t="s">
         <v>516</v>
       </c>
@@ -25722,7 +25707,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="749" spans="1:9" hidden="1">
+    <row r="749" spans="1:9">
       <c r="A749" s="19" t="s">
         <v>514</v>
       </c>
@@ -25745,7 +25730,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="750" spans="1:9" hidden="1">
+    <row r="750" spans="1:9">
       <c r="A750" s="22" t="s">
         <v>512</v>
       </c>
@@ -25768,7 +25753,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="751" spans="1:9" hidden="1">
+    <row r="751" spans="1:9">
       <c r="A751" s="19" t="s">
         <v>1146</v>
       </c>
@@ -25791,7 +25776,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="752" spans="1:9" hidden="1">
+    <row r="752" spans="1:9">
       <c r="A752" s="26" t="s">
         <v>1144</v>
       </c>
@@ -25816,7 +25801,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="753" spans="1:9" hidden="1">
+    <row r="753" spans="1:9">
       <c r="A753" s="19" t="s">
         <v>1142</v>
       </c>
@@ -25841,7 +25826,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="754" spans="1:9" hidden="1">
+    <row r="754" spans="1:9">
       <c r="A754" s="26" t="s">
         <v>717</v>
       </c>
@@ -25864,7 +25849,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="755" spans="1:9" hidden="1">
+    <row r="755" spans="1:9">
       <c r="A755" s="19" t="s">
         <v>1633</v>
       </c>
@@ -25887,7 +25872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" spans="1:9" hidden="1">
+    <row r="756" spans="1:9">
       <c r="A756" s="22" t="s">
         <v>1140</v>
       </c>
@@ -25910,7 +25895,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="757" spans="1:9" hidden="1">
+    <row r="757" spans="1:9">
       <c r="A757" s="19" t="s">
         <v>1138</v>
       </c>
@@ -25935,7 +25920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" spans="1:9" ht="15.75" hidden="1">
+    <row r="758" spans="1:9" ht="15.75">
       <c r="A758" s="22" t="s">
         <v>1136</v>
       </c>
@@ -25960,7 +25945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" spans="1:9" hidden="1">
+    <row r="759" spans="1:9">
       <c r="A759" s="19" t="s">
         <v>74</v>
       </c>
@@ -25985,7 +25970,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="760" spans="1:9" hidden="1">
+    <row r="760" spans="1:9">
       <c r="A760" s="22" t="s">
         <v>1134</v>
       </c>
@@ -26012,7 +25997,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="761" spans="1:9" hidden="1">
+    <row r="761" spans="1:9">
       <c r="A761" s="19" t="s">
         <v>1133</v>
       </c>
@@ -26035,7 +26020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="762" spans="1:9" hidden="1">
+    <row r="762" spans="1:9">
       <c r="A762" s="22" t="s">
         <v>1131</v>
       </c>
@@ -26058,7 +26043,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="763" spans="1:9" hidden="1">
+    <row r="763" spans="1:9">
       <c r="A763" s="19" t="s">
         <v>1129</v>
       </c>
@@ -26083,7 +26068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="764" spans="1:9" hidden="1">
+    <row r="764" spans="1:9">
       <c r="A764" s="26" t="s">
         <v>154</v>
       </c>
@@ -26106,7 +26091,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="765" spans="1:9" hidden="1">
+    <row r="765" spans="1:9">
       <c r="A765" s="19" t="s">
         <v>1127</v>
       </c>
@@ -26133,7 +26118,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="766" spans="1:9" hidden="1">
+    <row r="766" spans="1:9">
       <c r="A766" s="26" t="s">
         <v>713</v>
       </c>
@@ -26156,7 +26141,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="767" spans="1:9" hidden="1">
+    <row r="767" spans="1:9">
       <c r="A767" s="19" t="s">
         <v>504</v>
       </c>
@@ -26179,7 +26164,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="768" spans="1:9" hidden="1">
+    <row r="768" spans="1:9">
       <c r="A768" s="22" t="s">
         <v>1627</v>
       </c>
@@ -26202,7 +26187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="769" spans="1:9" hidden="1">
+    <row r="769" spans="1:9">
       <c r="A769" s="19" t="s">
         <v>72</v>
       </c>
@@ -26225,7 +26210,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="770" spans="1:9" hidden="1">
+    <row r="770" spans="1:9">
       <c r="A770" s="22" t="s">
         <v>500</v>
       </c>
@@ -26250,7 +26235,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="771" spans="1:9" hidden="1">
+    <row r="771" spans="1:9">
       <c r="A771" s="19" t="s">
         <v>1118</v>
       </c>
@@ -26275,7 +26260,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="772" spans="1:9" hidden="1">
+    <row r="772" spans="1:9">
       <c r="A772" s="26" t="s">
         <v>1116</v>
       </c>
@@ -26298,7 +26283,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="773" spans="1:9" hidden="1">
+    <row r="773" spans="1:9">
       <c r="A773" s="19" t="s">
         <v>1114</v>
       </c>
@@ -26323,7 +26308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="774" spans="1:9" hidden="1">
+    <row r="774" spans="1:9">
       <c r="A774" s="26" t="s">
         <v>1112</v>
       </c>
@@ -26346,7 +26331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="775" spans="1:9" hidden="1">
+    <row r="775" spans="1:9">
       <c r="A775" s="19" t="s">
         <v>1110</v>
       </c>
@@ -26369,7 +26354,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="776" spans="1:9" hidden="1">
+    <row r="776" spans="1:9">
       <c r="A776" s="22" t="s">
         <v>1106</v>
       </c>
@@ -26392,7 +26377,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="777" spans="1:9" hidden="1">
+    <row r="777" spans="1:9">
       <c r="A777" s="19" t="s">
         <v>1104</v>
       </c>
@@ -26417,7 +26402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="778" spans="1:9" hidden="1">
+    <row r="778" spans="1:9">
       <c r="A778" s="22" t="s">
         <v>1102</v>
       </c>
@@ -26440,7 +26425,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="779" spans="1:9" hidden="1">
+    <row r="779" spans="1:9">
       <c r="A779" s="19" t="s">
         <v>1100</v>
       </c>
@@ -26463,7 +26448,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="780" spans="1:9" hidden="1">
+    <row r="780" spans="1:9">
       <c r="A780" s="22" t="s">
         <v>1098</v>
       </c>
@@ -26486,7 +26471,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="781" spans="1:9" hidden="1">
+    <row r="781" spans="1:9">
       <c r="A781" s="23" t="s">
         <v>146</v>
       </c>
@@ -26509,7 +26494,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="782" spans="1:9" hidden="1">
+    <row r="782" spans="1:9">
       <c r="A782" s="49" t="s">
         <v>1096</v>
       </c>
@@ -26534,7 +26519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="783" spans="1:9" hidden="1">
+    <row r="783" spans="1:9">
       <c r="A783" s="51" t="s">
         <v>1092</v>
       </c>
@@ -26557,7 +26542,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="784" spans="1:9" hidden="1">
+    <row r="784" spans="1:9">
       <c r="A784" s="50" t="s">
         <v>1090</v>
       </c>
@@ -26580,7 +26565,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="785" spans="1:9" hidden="1">
+    <row r="785" spans="1:9">
       <c r="A785" s="51" t="s">
         <v>1668</v>
       </c>
@@ -26607,7 +26592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="786" spans="1:9" hidden="1">
+    <row r="786" spans="1:9">
       <c r="A786" s="54" t="s">
         <v>1670</v>
       </c>
@@ -26634,7 +26619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="787" spans="1:9" ht="15.75" hidden="1">
+    <row r="787" spans="1:9" ht="15.75">
       <c r="A787" s="55" t="s">
         <v>1672</v>
       </c>
@@ -26661,7 +26646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="788" spans="1:9" hidden="1">
+    <row r="788" spans="1:9">
       <c r="A788" s="56" t="s">
         <v>1676</v>
       </c>
@@ -26869,21 +26854,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010002AF94A3640FDE4F9838D663AA634D6E" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="010e943a03c7bfe98bea01de04df2ad0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="500d996f-f1f4-4aa2-9056-76b25a0746a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0cbd24a5130302e86adf8228cffd0913" ns2:_="">
     <xsd:import namespace="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
@@ -27021,31 +26991,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499146DB-7450-4136-823E-A20977BC98D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27061,4 +27022,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889B942-4E8E-45E8-893E-82EC9F551C9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2F003A-00AA-4592-A68B-47C8E5C543EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="500d996f-f1f4-4aa2-9056-76b25a0746a4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>